--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_41.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_12_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3094414.451618249</v>
+        <v>3095427.784849506</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13614470.20926906</v>
+        <v>13633690.08805694</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13614470.20926906</v>
+        <v>13633690.08805694</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143876.6510563084</v>
+        <v>143186.9484572015</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143876.6510563084</v>
+        <v>143186.9484572015</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25940050.88547231</v>
+        <v>25940028.20181233</v>
       </c>
     </row>
   </sheetData>
@@ -669,7 +669,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.343301935256381</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
         <v>3.769060713577687</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.36594612241183</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T2" t="n">
         <v>184.8629887637397</v>
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>169.5689676906451</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>128.4331699661508</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.4985557026693</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.44885845517734</v>
+        <v>374</v>
       </c>
       <c r="T3" t="n">
         <v>4.464774651476091</v>
@@ -793,7 +793,7 @@
         <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>374</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>133.5184388018132</v>
@@ -1024,22 +1024,22 @@
         <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>374</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
         <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
+        <v>14.51066719152016</v>
+      </c>
+      <c r="W6" t="n">
+        <v>114.0827611263746</v>
+      </c>
+      <c r="X6" t="n">
         <v>374</v>
       </c>
-      <c r="W6" t="n">
-        <v>32.37314290982852</v>
-      </c>
-      <c r="X6" t="n">
-        <v>329.8860968558554</v>
-      </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.953406460791602</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.41253966161941</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T8" t="n">
         <v>184.8629887637397</v>
@@ -1213,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>133.5184388018132</v>
+        <v>374</v>
       </c>
       <c r="S9" t="n">
         <v>62.44885845517734</v>
@@ -1267,16 +1267,16 @@
         <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>374</v>
+        <v>285.128676363185</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>337.931725668819</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1386,7 +1386,7 @@
         <v>72.59985970855254</v>
       </c>
       <c r="I11" t="n">
-        <v>1.388898923102739</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1425,7 +1425,7 @@
         <v>328.1087337345403</v>
       </c>
       <c r="V11" t="n">
-        <v>308.8510241668239</v>
+        <v>310.2399230899266</v>
       </c>
       <c r="W11" t="n">
         <v>317.3734759809475</v>
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>256.2832743226397</v>
+        <v>256.28327432264</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
         <v>3.986705686348098</v>
       </c>
       <c r="H12" t="n">
-        <v>3.897332469439999</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,7 +1498,7 @@
         <v>131.5805093985736</v>
       </c>
       <c r="T12" t="n">
-        <v>81.32333125524967</v>
+        <v>402.3233312552497</v>
       </c>
       <c r="U12" t="n">
         <v>79.16083145829995</v>
@@ -1620,10 +1620,10 @@
         <v>81.35033711113681</v>
       </c>
       <c r="H14" t="n">
-        <v>72.59985970855254</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I14" t="n">
-        <v>1.388898923102739</v>
+        <v>1.388898923102767</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>141.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T14" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U14" t="n">
-        <v>328.1087337345403</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V14" t="n">
         <v>308.8510241668239</v>
@@ -1684,7 +1684,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
         <v>26.93768689770263</v>
@@ -1693,13 +1693,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>3.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H15" t="n">
-        <v>3.897332469439999</v>
+        <v>3.897332469440016</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1732,25 +1732,25 @@
         <v>179.532287858417</v>
       </c>
       <c r="S15" t="n">
-        <v>131.5805093985736</v>
+        <v>452.5805093985736</v>
       </c>
       <c r="T15" t="n">
-        <v>81.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V15" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>291.5894571217006</v>
       </c>
       <c r="Y15" t="n">
-        <v>271.1181104424475</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M16" t="n">
         <v>100.6963655009106</v>
@@ -1811,7 +1811,7 @@
         <v>377.2234394565609</v>
       </c>
       <c r="S16" t="n">
-        <v>30.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1890,13 +1890,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>141.7853537319712</v>
+        <v>143.1742526550738</v>
       </c>
       <c r="T17" t="n">
         <v>259.5162852461518</v>
       </c>
       <c r="U17" t="n">
-        <v>329.497632657643</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V17" t="n">
         <v>308.8510241668239</v>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
         <v>21.67209722191262</v>
@@ -1933,13 +1933,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>3.986705686348103</v>
+        <v>5.506848792067714</v>
       </c>
       <c r="H18" t="n">
         <v>324.89733246944</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1975,19 +1975,19 @@
         <v>81.32333125524968</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16083145829998</v>
+        <v>400.1608314583</v>
       </c>
       <c r="V18" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>304.0998605861415</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.388898923102697</v>
       </c>
       <c r="S20" t="n">
-        <v>143.1742526550738</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T20" t="n">
         <v>259.5162852461518</v>
@@ -2158,13 +2158,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>232.8266301218324</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>179.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S21" t="n">
         <v>131.5805093985736</v>
@@ -2215,13 +2215,13 @@
         <v>79.16083145829998</v>
       </c>
       <c r="V21" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W21" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>98.86273944538755</v>
+        <v>291.5894571217008</v>
       </c>
       <c r="Y21" t="n">
         <v>78.39139276613435</v>
@@ -2410,10 +2410,10 @@
         <v>3.986705686348103</v>
       </c>
       <c r="H24" t="n">
-        <v>3.897332469440016</v>
+        <v>5.417475575159462</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>179.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S24" t="n">
         <v>131.5805093985736</v>
@@ -2452,16 +2452,16 @@
         <v>79.16083145829998</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>271.1181104424475</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>161.9993129555745</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>128.505877166097</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>90.33915573984979</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E26" t="n">
-        <v>84.36328960686865</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>84.88962870801186</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>82.35033711113681</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H26" t="n">
-        <v>73.59985970855254</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2598,28 +2598,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5.269698923102768</v>
       </c>
       <c r="S26" t="n">
-        <v>142.7853537319711</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T26" t="n">
-        <v>260.5162852461518</v>
+        <v>259.5162852461518</v>
       </c>
       <c r="U26" t="n">
-        <v>329.1087337345403</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V26" t="n">
-        <v>309.8510241668239</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>318.3734759809475</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>272.2818334606677</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>191.3174326828064</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64.55655664632661</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>27.93768689770263</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>22.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>211.3629600141898</v>
       </c>
       <c r="G27" t="n">
         <v>324.9867056863481</v>
       </c>
       <c r="H27" t="n">
-        <v>4.897332469439999</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>361.2590055347306</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S27" t="n">
-        <v>132.5805093985736</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T27" t="n">
-        <v>82.32333125524967</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U27" t="n">
-        <v>80.16083145829995</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V27" t="n">
-        <v>94.51066719152016</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>112.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>99.86273944538755</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>79.39139276613435</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,28 +2738,28 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M28" t="n">
-        <v>98.72043924187921</v>
+        <v>100.6963655009106</v>
       </c>
       <c r="N28" t="n">
-        <v>154.602288386439</v>
+        <v>153.602288386439</v>
       </c>
       <c r="O28" t="n">
-        <v>231.2357280134412</v>
+        <v>230.2357280134412</v>
       </c>
       <c r="P28" t="n">
-        <v>291.1134710987693</v>
+        <v>290.1134710987693</v>
       </c>
       <c r="Q28" t="n">
-        <v>352.989266425598</v>
+        <v>351.989266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>378.2234394565609</v>
+        <v>377.2234394565609</v>
       </c>
       <c r="S28" t="n">
-        <v>31.37429937498658</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2787,28 +2787,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>161.9993129555745</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>129.4745782429939</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>90.33915573984979</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E29" t="n">
-        <v>84.36328960686865</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>83.92092763111485</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>82.35033711113681</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H29" t="n">
-        <v>73.59985970855254</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5.269698923102741</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2838,25 +2838,25 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>142.7853537319711</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T29" t="n">
-        <v>260.5162852461518</v>
+        <v>259.5162852461518</v>
       </c>
       <c r="U29" t="n">
-        <v>329.1087337345403</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V29" t="n">
-        <v>309.8510241668239</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>318.3734759809475</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>272.2818334606677</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>191.3174326828064</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64.55655664632661</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>41.09991244551929</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>22.67209722191262</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>4.986705686348098</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H30" t="n">
-        <v>314.4174755751598</v>
+        <v>5.417475575159603</v>
       </c>
       <c r="I30" t="n">
         <v>191.2065745705938</v>
@@ -2914,28 +2914,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>180.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S30" t="n">
-        <v>132.5805093985736</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T30" t="n">
-        <v>82.32333125524967</v>
+        <v>402.3233312552497</v>
       </c>
       <c r="U30" t="n">
-        <v>80.16083145829995</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V30" t="n">
-        <v>94.51066719152016</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>112.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>99.86273944538755</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>79.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="31">
@@ -2975,28 +2975,28 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M31" t="n">
-        <v>98.72043924187921</v>
+        <v>100.6963655009106</v>
       </c>
       <c r="N31" t="n">
-        <v>154.602288386439</v>
+        <v>153.602288386439</v>
       </c>
       <c r="O31" t="n">
-        <v>231.2357280134412</v>
+        <v>230.2357280134412</v>
       </c>
       <c r="P31" t="n">
-        <v>291.1134710987693</v>
+        <v>290.1134710987693</v>
       </c>
       <c r="Q31" t="n">
-        <v>352.989266425598</v>
+        <v>351.989266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>378.2234394565609</v>
+        <v>377.2234394565609</v>
       </c>
       <c r="S31" t="n">
-        <v>31.37429937498658</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3024,25 +3024,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>161.9993129555745</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C32" t="n">
-        <v>129.4745782429939</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>90.33915573984979</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E32" t="n">
-        <v>84.36328960686865</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>84.88962870801186</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.3816360342398</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H32" t="n">
-        <v>73.59985970855254</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3075,25 +3075,25 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>142.7853537319711</v>
+        <v>147.0550526550739</v>
       </c>
       <c r="T32" t="n">
-        <v>260.5162852461518</v>
+        <v>259.5162852461518</v>
       </c>
       <c r="U32" t="n">
-        <v>329.1087337345403</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V32" t="n">
-        <v>309.8510241668239</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>318.3734759809475</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>272.2818334606677</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>191.3174326828064</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64.55655664632661</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>27.93768689770263</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>4.986705686348098</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H33" t="n">
-        <v>185.6240501457537</v>
+        <v>3.897332469439999</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,31 +3148,31 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R33" t="n">
-        <v>180.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S33" t="n">
-        <v>132.5805093985736</v>
+        <v>452.5805093985736</v>
       </c>
       <c r="T33" t="n">
-        <v>82.32333125524967</v>
+        <v>402.3233312552497</v>
       </c>
       <c r="U33" t="n">
-        <v>80.16083145829995</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V33" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>112.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>99.86273944538755</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>79.39139276613435</v>
+        <v>194.1369585595152</v>
       </c>
     </row>
     <row r="34">
@@ -3212,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M34" t="n">
-        <v>98.72043924187921</v>
+        <v>100.6963655009106</v>
       </c>
       <c r="N34" t="n">
-        <v>154.602288386439</v>
+        <v>153.602288386439</v>
       </c>
       <c r="O34" t="n">
-        <v>231.2357280134412</v>
+        <v>230.2357280134412</v>
       </c>
       <c r="P34" t="n">
-        <v>291.1134710987693</v>
+        <v>290.1134710987693</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.989266425598</v>
+        <v>351.989266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>378.2234394565609</v>
+        <v>377.2234394565609</v>
       </c>
       <c r="S34" t="n">
-        <v>31.37429937498658</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>-4.008246397435105e-11</v>
       </c>
       <c r="S35" t="n">
-        <v>117.5446526550742</v>
+        <v>117.7853537319711</v>
       </c>
       <c r="T35" t="n">
         <v>235.5162852461518</v>
@@ -3330,7 +3330,7 @@
         <v>247.2818334606677</v>
       </c>
       <c r="Y35" t="n">
-        <v>166.3174326828064</v>
+        <v>154.4343316059524</v>
       </c>
     </row>
     <row r="36">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>39.55655664632661</v>
       </c>
       <c r="C36" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>145.8504152735578</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3394,7 +3394,7 @@
         <v>107.5805093985736</v>
       </c>
       <c r="T36" t="n">
-        <v>61.02272109935815</v>
+        <v>57.32333125524966</v>
       </c>
       <c r="U36" t="n">
         <v>55.16083145829995</v>
@@ -3409,7 +3409,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>54.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -3513,7 +3513,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>57.35033711113681</v>
+        <v>45.46723603423965</v>
       </c>
       <c r="H38" t="n">
         <v>48.59985970855251</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>117.5446526550742</v>
+        <v>117.7853537319712</v>
       </c>
       <c r="T38" t="n">
         <v>235.5162852461518</v>
@@ -3583,7 +3583,7 @@
         <v>16.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3.699389844108131</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,28 +3625,28 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R39" t="n">
-        <v>155.532287858417</v>
+        <v>500.532287858417</v>
       </c>
       <c r="S39" t="n">
         <v>107.5805093985736</v>
       </c>
       <c r="T39" t="n">
-        <v>57.32333125524968</v>
+        <v>402.3233312552497</v>
       </c>
       <c r="U39" t="n">
         <v>55.16083145829998</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>54.39139276613435</v>
+        <v>66.55105014080249</v>
       </c>
     </row>
     <row r="40">
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>161.9993129555745</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>129.4745782429939</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>65.3015697975227</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>72.59985970855251</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,25 +3786,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>142.7853537319711</v>
+        <v>141.7853537319712</v>
       </c>
       <c r="T41" t="n">
-        <v>260.5162852461518</v>
+        <v>259.5162852461518</v>
       </c>
       <c r="U41" t="n">
-        <v>329.1087337345403</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>309.8510241668239</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>318.3734759809475</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>272.2818334606677</v>
+        <v>251.507466118311</v>
       </c>
       <c r="Y41" t="n">
-        <v>191.3174326828064</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3814,28 +3814,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>289.8569942042636</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>27.93768689770263</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>22.67209722191262</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>19.63624233787687</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>4.986705686348098</v>
+        <v>3.986705686348103</v>
       </c>
       <c r="H42" t="n">
         <v>324.89733246944</v>
       </c>
       <c r="I42" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,31 +3859,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>180.532287858417</v>
+        <v>353.3780518698796</v>
       </c>
       <c r="S42" t="n">
-        <v>132.5805093985736</v>
+        <v>452.5805093985736</v>
       </c>
       <c r="T42" t="n">
-        <v>82.32333125524967</v>
+        <v>81.32333125524968</v>
       </c>
       <c r="U42" t="n">
-        <v>80.16083145829995</v>
+        <v>79.16083145829998</v>
       </c>
       <c r="V42" t="n">
-        <v>94.51066719152016</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>112.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>99.86273944538755</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>79.39139276613435</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3923,28 +3923,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>9.713201928270976</v>
+        <v>8.713201928270962</v>
       </c>
       <c r="M43" t="n">
-        <v>101.6963655009106</v>
+        <v>100.6963655009106</v>
       </c>
       <c r="N43" t="n">
-        <v>141.9131601991368</v>
+        <v>153.602288386439</v>
       </c>
       <c r="O43" t="n">
-        <v>231.2357280134412</v>
+        <v>230.2357280134412</v>
       </c>
       <c r="P43" t="n">
-        <v>291.1134710987693</v>
+        <v>290.1134710987693</v>
       </c>
       <c r="Q43" t="n">
-        <v>352.989266425598</v>
+        <v>351.989266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>378.2234394565609</v>
+        <v>377.2234394565609</v>
       </c>
       <c r="S43" t="n">
-        <v>31.37429937498658</v>
+        <v>30.37429937498661</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,22 +3972,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>161.9993129555745</v>
+        <v>110.8647149260699</v>
       </c>
       <c r="C44" t="n">
-        <v>129.4745782429939</v>
+        <v>128.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>90.33915573984979</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>84.88962870801186</v>
+        <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>32.85813908163211</v>
+        <v>81.35033711113681</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4026,22 +4026,22 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>260.5162852461518</v>
+        <v>259.5162852461518</v>
       </c>
       <c r="U44" t="n">
-        <v>329.1087337345404</v>
+        <v>328.1087337345403</v>
       </c>
       <c r="V44" t="n">
-        <v>309.8510241668239</v>
+        <v>308.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>318.3734759809475</v>
+        <v>317.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>272.2818334606677</v>
+        <v>271.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>191.3174326828064</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64.55655664632661</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>116.1432544664077</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>4.986705686348103</v>
+        <v>3.986705686348098</v>
       </c>
       <c r="H45" t="n">
-        <v>4.897332469440016</v>
+        <v>324.89733246944</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>180.532287858417</v>
+        <v>179.532287858417</v>
       </c>
       <c r="S45" t="n">
-        <v>132.5805093985736</v>
+        <v>131.5805093985736</v>
       </c>
       <c r="T45" t="n">
-        <v>82.32333125524968</v>
+        <v>81.32333125524967</v>
       </c>
       <c r="U45" t="n">
-        <v>80.16083145829998</v>
+        <v>79.16083145829995</v>
       </c>
       <c r="V45" t="n">
-        <v>94.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>112.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>99.86273944538755</v>
+        <v>272.7085034568501</v>
       </c>
       <c r="Y45" t="n">
-        <v>79.39139276613435</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4160,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>8.713201928270976</v>
       </c>
       <c r="M46" t="n">
-        <v>98.72043924187943</v>
+        <v>100.6963655009106</v>
       </c>
       <c r="N46" t="n">
-        <v>154.602288386439</v>
+        <v>153.602288386439</v>
       </c>
       <c r="O46" t="n">
-        <v>231.2357280134412</v>
+        <v>230.2357280134412</v>
       </c>
       <c r="P46" t="n">
-        <v>291.1134710987693</v>
+        <v>290.1134710987693</v>
       </c>
       <c r="Q46" t="n">
-        <v>352.989266425598</v>
+        <v>351.989266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>378.2234394565609</v>
+        <v>377.2234394565609</v>
       </c>
       <c r="S46" t="n">
-        <v>31.37429937498661</v>
+        <v>30.37429937498658</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.8684999460185</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>56.89417848844885</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>46.45058683203492</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E2" t="n">
-        <v>42.04322359277366</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F2" t="n">
-        <v>37.10420469579199</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G2" t="n">
         <v>33.72713203391686</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>30.01969029977264</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>400.2796902997726</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>770.5396902997726</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="M2" t="n">
-        <v>1140.799690299772</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N2" t="n">
-        <v>1437.335793611129</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>1437.335793611129</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.751569573321</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.021277892776</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3160547407863</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1433030571258</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W2" t="n">
-        <v>496.3620141874817</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1379399847871</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.6960887900331</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>371.4650920747171</v>
+        <v>394.8673009400699</v>
       </c>
       <c r="C3" t="n">
-        <v>371.4650920747171</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="D3" t="n">
-        <v>371.4650920747171</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="E3" t="n">
-        <v>241.7346173614335</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="F3" t="n">
-        <v>241.7346173614335</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="G3" t="n">
-        <v>241.7346173614335</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="H3" t="n">
-        <v>241.7346173614335</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="I3" t="n">
         <v>30.1199146314645</v>
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.738421006376</v>
+        <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.871311105555</v>
+        <v>1361.132890099179</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.791656100326</v>
+        <v>983.3551123214008</v>
       </c>
       <c r="T3" t="n">
-        <v>1147.281782714996</v>
+        <v>978.8452389360715</v>
       </c>
       <c r="U3" t="n">
-        <v>1147.084020807432</v>
+        <v>978.6474770285072</v>
       </c>
       <c r="V3" t="n">
-        <v>769.3062430296541</v>
+        <v>963.9902374411131</v>
       </c>
       <c r="W3" t="n">
-        <v>391.5284652518762</v>
+        <v>586.2124596633353</v>
       </c>
       <c r="X3" t="n">
-        <v>371.4650920747171</v>
+        <v>566.1490864861761</v>
       </c>
       <c r="Y3" t="n">
-        <v>371.4650920747171</v>
+        <v>566.1490864861761</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.37478771712392</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="C4" t="n">
-        <v>70.37478771712392</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="D4" t="n">
-        <v>89.88467730995343</v>
+        <v>629.0765472024223</v>
       </c>
       <c r="E4" t="n">
-        <v>207.7135815213665</v>
+        <v>629.0765472024223</v>
       </c>
       <c r="F4" t="n">
-        <v>332.0745541133019</v>
+        <v>753.4375197943577</v>
       </c>
       <c r="G4" t="n">
-        <v>485.6650003280561</v>
+        <v>753.4375197943577</v>
       </c>
       <c r="H4" t="n">
-        <v>656.8164487661421</v>
+        <v>924.5889682324438</v>
       </c>
       <c r="I4" t="n">
-        <v>883.4791106530447</v>
+        <v>1151.251630119346</v>
       </c>
       <c r="J4" t="n">
-        <v>1253.739110653045</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="K4" t="n">
-        <v>1385.467095409585</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
         <v>1385.467095409585</v>
@@ -4512,19 +4512,19 @@
         <v>70.37478771712392</v>
       </c>
       <c r="U4" t="n">
-        <v>70.37478771712392</v>
+        <v>316.9360101914762</v>
       </c>
       <c r="V4" t="n">
-        <v>70.37478771712392</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="W4" t="n">
-        <v>70.37478771712392</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="X4" t="n">
-        <v>70.37478771712392</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="Y4" t="n">
-        <v>70.37478771712392</v>
+        <v>515.7574030774222</v>
       </c>
     </row>
     <row r="5">
@@ -4658,31 +4658,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1349.538506374912</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1214.671396474091</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1151.591741468861</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
-        <v>773.8139636910835</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U6" t="n">
-        <v>773.6162017835192</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V6" t="n">
-        <v>395.8384240057413</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W6" t="n">
-        <v>363.1382796523792</v>
+        <v>1163.253333333334</v>
       </c>
       <c r="X6" t="n">
-        <v>29.92</v>
+        <v>785.4755555555557</v>
       </c>
       <c r="Y6" t="n">
-        <v>29.92</v>
+        <v>407.6977777777778</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141.6773376662921</v>
+        <v>353.6750066558336</v>
       </c>
       <c r="C7" t="n">
-        <v>267.679343484728</v>
+        <v>353.6750066558336</v>
       </c>
       <c r="D7" t="n">
-        <v>380.998487609728</v>
+        <v>353.6750066558336</v>
       </c>
       <c r="E7" t="n">
-        <v>498.8273918211411</v>
+        <v>353.6750066558336</v>
       </c>
       <c r="F7" t="n">
-        <v>623.1883644130766</v>
+        <v>353.6750066558336</v>
       </c>
       <c r="G7" t="n">
-        <v>776.7788106278307</v>
+        <v>507.2654528705878</v>
       </c>
       <c r="H7" t="n">
-        <v>947.9302590659167</v>
+        <v>678.4169013086738</v>
       </c>
       <c r="I7" t="n">
-        <v>1174.592920952819</v>
+        <v>905.0795631955764</v>
       </c>
       <c r="J7" t="n">
-        <v>1385.467095409585</v>
+        <v>1275.339563195576</v>
       </c>
       <c r="K7" t="n">
         <v>1385.467095409585</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="V7" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="W7" t="n">
-        <v>29.92</v>
+        <v>242.2657059768013</v>
       </c>
       <c r="X7" t="n">
-        <v>29.92</v>
+        <v>242.2657059768013</v>
       </c>
       <c r="Y7" t="n">
-        <v>29.92</v>
+        <v>353.6750066558336</v>
       </c>
     </row>
     <row r="8">
@@ -4795,19 +4795,19 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>30.01969029977264</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>400.2796902997726</v>
+        <v>696.8157936111289</v>
       </c>
       <c r="L8" t="n">
-        <v>770.5396902997726</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="M8" t="n">
-        <v>770.5396902997726</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>1140.799690299772</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O8" t="n">
         <v>1437.335793611129</v>
@@ -4819,7 +4819,7 @@
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1494.026862160817</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
         <v>1407.751569573322</v>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>727.505640524864</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>727.505640524864</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E9" t="n">
         <v>29.92</v>
@@ -4889,37 +4889,37 @@
         <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1341.388006370726</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1495.800085368534</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1349.538506374911</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1214.67139647409</v>
+        <v>1118.022307590758</v>
       </c>
       <c r="S9" t="n">
-        <v>1151.59174146886</v>
+        <v>1054.942652585528</v>
       </c>
       <c r="T9" t="n">
-        <v>1147.08186808353</v>
+        <v>1050.432779200199</v>
       </c>
       <c r="U9" t="n">
-        <v>1146.884106175966</v>
+        <v>1050.235017292634</v>
       </c>
       <c r="V9" t="n">
-        <v>769.1063283981885</v>
+        <v>1035.57777770524</v>
       </c>
       <c r="W9" t="n">
-        <v>391.3285506204106</v>
+        <v>747.5690137020232</v>
       </c>
       <c r="X9" t="n">
-        <v>371.2651774432515</v>
+        <v>727.505640524864</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.92</v>
+        <v>727.505640524864</v>
       </c>
     </row>
     <row r="10">
@@ -4929,22 +4929,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>428.3453108705084</v>
+        <v>531.9843092935555</v>
       </c>
       <c r="C10" t="n">
-        <v>428.3453108705084</v>
+        <v>657.9863151119913</v>
       </c>
       <c r="D10" t="n">
-        <v>428.3453108705084</v>
+        <v>657.9863151119913</v>
       </c>
       <c r="E10" t="n">
-        <v>430.3504054484048</v>
+        <v>657.9863151119913</v>
       </c>
       <c r="F10" t="n">
-        <v>554.7113780403403</v>
+        <v>782.3472877039268</v>
       </c>
       <c r="G10" t="n">
-        <v>708.3018242550944</v>
+        <v>782.3472877039268</v>
       </c>
       <c r="H10" t="n">
         <v>879.4532726931805</v>
@@ -4986,19 +4986,19 @@
         <v>70.37478771712392</v>
       </c>
       <c r="U10" t="n">
-        <v>316.9360101914762</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="V10" t="n">
-        <v>316.9360101914762</v>
+        <v>269.1961806030699</v>
       </c>
       <c r="W10" t="n">
-        <v>316.9360101914762</v>
+        <v>269.1961806030699</v>
       </c>
       <c r="X10" t="n">
-        <v>316.9360101914762</v>
+        <v>420.2269716272634</v>
       </c>
       <c r="Y10" t="n">
-        <v>428.3453108705084</v>
+        <v>420.2269716272634</v>
       </c>
     </row>
     <row r="11">
@@ -5008,25 +5008,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.7843919601175</v>
+        <v>596.3814637549632</v>
       </c>
       <c r="C11" t="n">
-        <v>468.0120907045681</v>
+        <v>466.6091624994138</v>
       </c>
       <c r="D11" t="n">
-        <v>377.7705192501743</v>
+        <v>376.36759104502</v>
       </c>
       <c r="E11" t="n">
-        <v>293.5651762129333</v>
+        <v>292.162248007779</v>
       </c>
       <c r="F11" t="n">
-        <v>208.8281775179718</v>
+        <v>207.4252493128175</v>
       </c>
       <c r="G11" t="n">
-        <v>126.6561198299548</v>
+        <v>125.2531916248006</v>
       </c>
       <c r="H11" t="n">
-        <v>53.32292820515428</v>
+        <v>51.92</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
@@ -5035,16 +5035,16 @@
         <v>135.4535720585666</v>
       </c>
       <c r="K11" t="n">
-        <v>777.9635720585666</v>
+        <v>312.6439213047977</v>
       </c>
       <c r="L11" t="n">
-        <v>1420.473572058567</v>
+        <v>532.4642177872098</v>
       </c>
       <c r="M11" t="n">
-        <v>1588.310595394003</v>
+        <v>1110.954106525702</v>
       </c>
       <c r="N11" t="n">
-        <v>2230.820595394003</v>
+        <v>1753.464106525702</v>
       </c>
       <c r="O11" t="n">
         <v>2395.974106525702</v>
@@ -5068,16 +5068,16 @@
         <v>1859.221845744784</v>
       </c>
       <c r="V11" t="n">
-        <v>1547.251114263144</v>
+        <v>1545.84818605799</v>
       </c>
       <c r="W11" t="n">
-        <v>1226.67184559552</v>
+        <v>1225.268917390366</v>
       </c>
       <c r="X11" t="n">
-        <v>952.6497915948457</v>
+        <v>951.2468633896915</v>
       </c>
       <c r="Y11" t="n">
-        <v>760.4099606021121</v>
+        <v>759.0070323969577</v>
       </c>
     </row>
     <row r="12">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1141.041188948283</v>
+        <v>816.7987647058582</v>
       </c>
       <c r="C12" t="n">
-        <v>1100.536226882101</v>
+        <v>776.2938026396771</v>
       </c>
       <c r="D12" t="n">
         <v>749.084017894523</v>
@@ -5099,10 +5099,10 @@
         <v>402.9505863572374</v>
       </c>
       <c r="F12" t="n">
-        <v>59.88367490483647</v>
+        <v>384.1260991472608</v>
       </c>
       <c r="G12" t="n">
-        <v>55.85669946408081</v>
+        <v>380.0991237065051</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5141,22 +5141,22 @@
         <v>1948.016319603899</v>
       </c>
       <c r="T12" t="n">
-        <v>1865.871540558192</v>
+        <v>1541.629116315768</v>
       </c>
       <c r="U12" t="n">
-        <v>1785.911104741727</v>
+        <v>1461.668680499303</v>
       </c>
       <c r="V12" t="n">
-        <v>1691.455885356353</v>
+        <v>1367.213461113929</v>
       </c>
       <c r="W12" t="n">
-        <v>1578.957761205011</v>
+        <v>1254.715336962587</v>
       </c>
       <c r="X12" t="n">
-        <v>1479.096408229872</v>
+        <v>1154.853983987448</v>
       </c>
       <c r="Y12" t="n">
-        <v>1399.913183213575</v>
+        <v>1075.670758971151</v>
       </c>
     </row>
     <row r="13">
@@ -5263,31 +5263,31 @@
         <v>126.6561198299548</v>
       </c>
       <c r="H14" t="n">
-        <v>53.32292820515428</v>
+        <v>53.32292820515431</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>561.4552612788618</v>
+        <v>135.4535720585666</v>
       </c>
       <c r="K14" t="n">
-        <v>999.286970190582</v>
+        <v>448.6497035175879</v>
       </c>
       <c r="L14" t="n">
-        <v>1641.796970190582</v>
+        <v>668.47</v>
       </c>
       <c r="M14" t="n">
-        <v>1641.796970190582</v>
+        <v>1310.98</v>
       </c>
       <c r="N14" t="n">
-        <v>1641.796970190582</v>
+        <v>1310.98</v>
       </c>
       <c r="O14" t="n">
-        <v>1806.950481322281</v>
+        <v>1953.49</v>
       </c>
       <c r="P14" t="n">
-        <v>2006.976374796579</v>
+        <v>2596</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>168.3139162210096</v>
+        <v>816.7987647058583</v>
       </c>
       <c r="C15" t="n">
-        <v>127.8089541548285</v>
+        <v>452.0513783972528</v>
       </c>
       <c r="D15" t="n">
-        <v>100.5991694096743</v>
+        <v>424.8415936520987</v>
       </c>
       <c r="E15" t="n">
-        <v>78.70816211481309</v>
+        <v>402.9505863572374</v>
       </c>
       <c r="F15" t="n">
-        <v>59.88367490483647</v>
+        <v>59.88367490483648</v>
       </c>
       <c r="G15" t="n">
-        <v>55.85669946408081</v>
+        <v>55.85669946408083</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5375,25 +5375,25 @@
         <v>2080.925925057003</v>
       </c>
       <c r="S15" t="n">
-        <v>1948.016319603899</v>
+        <v>1623.773895361475</v>
       </c>
       <c r="T15" t="n">
-        <v>1865.871540558192</v>
+        <v>1541.629116315768</v>
       </c>
       <c r="U15" t="n">
-        <v>1785.911104741727</v>
+        <v>1461.668680499303</v>
       </c>
       <c r="V15" t="n">
         <v>1367.213461113929</v>
       </c>
       <c r="W15" t="n">
-        <v>930.4729127201629</v>
+        <v>1254.715336962587</v>
       </c>
       <c r="X15" t="n">
-        <v>506.3691355025996</v>
+        <v>960.1805317891522</v>
       </c>
       <c r="Y15" t="n">
-        <v>232.5124582880062</v>
+        <v>880.9973067728548</v>
       </c>
     </row>
     <row r="16">
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>675.5869414962938</v>
+        <v>686.6904483778065</v>
       </c>
       <c r="C16" t="n">
-        <v>723.3789473147295</v>
+        <v>734.4824541962423</v>
       </c>
       <c r="D16" t="n">
         <v>758.4880914397296</v>
@@ -5448,31 +5448,31 @@
         <v>819.1796012698439</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.6348877086339</v>
+        <v>463.6348877086338</v>
       </c>
       <c r="R16" t="n">
-        <v>82.60111047978444</v>
+        <v>82.60111047978445</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
       </c>
       <c r="T16" t="n">
-        <v>153.3519263756527</v>
+        <v>164.4554332571655</v>
       </c>
       <c r="U16" t="n">
-        <v>321.7272009811524</v>
+        <v>332.8307078626652</v>
       </c>
       <c r="V16" t="n">
-        <v>442.3385938670984</v>
+        <v>453.4421007486112</v>
       </c>
       <c r="W16" t="n">
-        <v>536.0195121267758</v>
+        <v>547.1230190082886</v>
       </c>
       <c r="X16" t="n">
-        <v>608.8403031509694</v>
+        <v>619.9438100324821</v>
       </c>
       <c r="Y16" t="n">
-        <v>642.0396038300016</v>
+        <v>653.1431107115144</v>
       </c>
     </row>
     <row r="17">
@@ -5509,22 +5509,22 @@
         <v>561.4552612788618</v>
       </c>
       <c r="K17" t="n">
-        <v>1203.965261278862</v>
+        <v>738.645610525093</v>
       </c>
       <c r="L17" t="n">
-        <v>1588.310595394003</v>
+        <v>958.4659070075052</v>
       </c>
       <c r="M17" t="n">
-        <v>1588.310595394003</v>
+        <v>999.286970190582</v>
       </c>
       <c r="N17" t="n">
-        <v>2230.820595394003</v>
+        <v>1641.796970190582</v>
       </c>
       <c r="O17" t="n">
-        <v>2395.974106525702</v>
+        <v>1806.950481322281</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2006.976374796579</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
@@ -5533,10 +5533,10 @@
         <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.782470977807</v>
+        <v>2451.379542772653</v>
       </c>
       <c r="T17" t="n">
-        <v>2190.644809113007</v>
+        <v>2189.241880907853</v>
       </c>
       <c r="U17" t="n">
         <v>1857.81891753963</v>
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>492.556340463434</v>
+        <v>1011.472216904154</v>
       </c>
       <c r="C18" t="n">
-        <v>452.0513783972528</v>
+        <v>970.9672548379733</v>
       </c>
       <c r="D18" t="n">
-        <v>424.8415936520987</v>
+        <v>619.5150458503949</v>
       </c>
       <c r="E18" t="n">
-        <v>402.9505863572374</v>
+        <v>597.6240385555337</v>
       </c>
       <c r="F18" t="n">
-        <v>384.1260991472608</v>
+        <v>578.7995513455571</v>
       </c>
       <c r="G18" t="n">
-        <v>380.0991237065051</v>
+        <v>573.237077818216</v>
       </c>
       <c r="H18" t="n">
-        <v>51.92</v>
+        <v>245.057954111711</v>
       </c>
       <c r="I18" t="n">
         <v>51.92</v>
@@ -5618,19 +5618,19 @@
         <v>1865.871540558192</v>
       </c>
       <c r="U18" t="n">
-        <v>1785.911104741727</v>
+        <v>1461.668680499303</v>
       </c>
       <c r="V18" t="n">
-        <v>1691.455885356353</v>
+        <v>1367.213461113929</v>
       </c>
       <c r="W18" t="n">
-        <v>1384.284309006715</v>
+        <v>1254.715336962587</v>
       </c>
       <c r="X18" t="n">
-        <v>1284.422956031576</v>
+        <v>1154.853983987448</v>
       </c>
       <c r="Y18" t="n">
-        <v>880.9973067728548</v>
+        <v>1075.670758971151</v>
       </c>
     </row>
     <row r="19">
@@ -5706,7 +5706,7 @@
         <v>547.1230190082886</v>
       </c>
       <c r="X19" t="n">
-        <v>619.9438100324821</v>
+        <v>608.8403031509694</v>
       </c>
       <c r="Y19" t="n">
         <v>642.0396038300016</v>
@@ -5743,31 +5743,31 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>561.4552612788618</v>
+        <v>135.4535720585666</v>
       </c>
       <c r="K20" t="n">
-        <v>1203.965261278862</v>
+        <v>777.9635720585666</v>
       </c>
       <c r="L20" t="n">
-        <v>1846.475261278862</v>
+        <v>1420.473572058567</v>
       </c>
       <c r="M20" t="n">
-        <v>1846.475261278862</v>
+        <v>1420.473572058567</v>
       </c>
       <c r="N20" t="n">
-        <v>1846.475261278862</v>
+        <v>2062.983572058567</v>
       </c>
       <c r="O20" t="n">
-        <v>2011.62877241056</v>
+        <v>2395.974106525702</v>
       </c>
       <c r="P20" t="n">
-        <v>2211.654665884859</v>
+        <v>2596</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2596</v>
+        <v>2594.597071794846</v>
       </c>
       <c r="S20" t="n">
         <v>2451.379542772653</v>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1335.714641146579</v>
+        <v>492.556340463434</v>
       </c>
       <c r="C21" t="n">
-        <v>1100.536226882101</v>
+        <v>452.0513783972528</v>
       </c>
       <c r="D21" t="n">
-        <v>749.084017894523</v>
+        <v>424.8415936520987</v>
       </c>
       <c r="E21" t="n">
         <v>402.9505863572374</v>
@@ -5846,28 +5846,28 @@
         <v>2262.271670368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2080.925925057003</v>
+        <v>1756.683500814579</v>
       </c>
       <c r="S21" t="n">
-        <v>1948.016319603899</v>
+        <v>1623.773895361475</v>
       </c>
       <c r="T21" t="n">
-        <v>1865.871540558192</v>
+        <v>1541.629116315768</v>
       </c>
       <c r="U21" t="n">
-        <v>1785.911104741727</v>
+        <v>1461.668680499303</v>
       </c>
       <c r="V21" t="n">
-        <v>1691.455885356353</v>
+        <v>1042.971036871505</v>
       </c>
       <c r="W21" t="n">
-        <v>1578.957761205011</v>
+        <v>930.4729127201631</v>
       </c>
       <c r="X21" t="n">
-        <v>1479.096408229872</v>
+        <v>635.9381075467279</v>
       </c>
       <c r="Y21" t="n">
-        <v>1399.913183213575</v>
+        <v>556.7548825304306</v>
       </c>
     </row>
     <row r="22">
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>686.6904483778065</v>
+        <v>675.5869414962938</v>
       </c>
       <c r="C22" t="n">
-        <v>734.4824541962423</v>
+        <v>723.3789473147295</v>
       </c>
       <c r="D22" t="n">
-        <v>769.5915983212424</v>
+        <v>758.4880914397296</v>
       </c>
       <c r="E22" t="n">
-        <v>809.2105025326554</v>
+        <v>798.1069956511426</v>
       </c>
       <c r="F22" t="n">
-        <v>855.3614751245908</v>
+        <v>844.257968243078</v>
       </c>
       <c r="G22" t="n">
-        <v>931.1828770770499</v>
+        <v>920.0793701955371</v>
       </c>
       <c r="H22" t="n">
-        <v>1028.044822892185</v>
+        <v>1016.941316010672</v>
       </c>
       <c r="I22" t="n">
-        <v>1189.758226418432</v>
+        <v>1178.654719536919</v>
       </c>
       <c r="J22" t="n">
-        <v>1516.807876906949</v>
+        <v>1505.704370025436</v>
       </c>
       <c r="K22" t="n">
         <v>1610.453394126239</v>
@@ -5931,22 +5931,22 @@
         <v>51.92</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4554332571655</v>
+        <v>153.3519263756527</v>
       </c>
       <c r="U22" t="n">
-        <v>332.8307078626652</v>
+        <v>321.7272009811524</v>
       </c>
       <c r="V22" t="n">
-        <v>453.4421007486112</v>
+        <v>442.3385938670984</v>
       </c>
       <c r="W22" t="n">
-        <v>547.1230190082886</v>
+        <v>536.0195121267758</v>
       </c>
       <c r="X22" t="n">
-        <v>619.9438100324821</v>
+        <v>608.8403031509694</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.1431107115144</v>
+        <v>642.0396038300016</v>
       </c>
     </row>
     <row r="23">
@@ -5980,22 +5980,22 @@
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>135.4535720585666</v>
+        <v>561.4552612788618</v>
       </c>
       <c r="K23" t="n">
-        <v>312.6439213047977</v>
+        <v>738.645610525093</v>
       </c>
       <c r="L23" t="n">
-        <v>945.8005953940028</v>
+        <v>958.4659070075052</v>
       </c>
       <c r="M23" t="n">
-        <v>1588.310595394003</v>
+        <v>958.4659070075052</v>
       </c>
       <c r="N23" t="n">
-        <v>2230.820595394003</v>
+        <v>1600.975907007505</v>
       </c>
       <c r="O23" t="n">
-        <v>2395.974106525702</v>
+        <v>1953.49</v>
       </c>
       <c r="P23" t="n">
         <v>2596</v>
@@ -6035,25 +6035,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.3139162210097</v>
+        <v>362.9873684193059</v>
       </c>
       <c r="C24" t="n">
-        <v>127.8089541548285</v>
+        <v>322.4824063531248</v>
       </c>
       <c r="D24" t="n">
-        <v>100.5991694096744</v>
+        <v>295.2726216079706</v>
       </c>
       <c r="E24" t="n">
-        <v>78.70816211481312</v>
+        <v>273.3816143131094</v>
       </c>
       <c r="F24" t="n">
-        <v>59.88367490483648</v>
+        <v>254.5571271031327</v>
       </c>
       <c r="G24" t="n">
-        <v>55.85669946408083</v>
+        <v>250.5301516623771</v>
       </c>
       <c r="H24" t="n">
-        <v>51.92</v>
+        <v>245.057954111711</v>
       </c>
       <c r="I24" t="n">
         <v>51.92</v>
@@ -6083,28 +6083,28 @@
         <v>2262.271670368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2080.925925057003</v>
+        <v>1756.683500814579</v>
       </c>
       <c r="S24" t="n">
-        <v>1948.016319603899</v>
+        <v>1623.773895361475</v>
       </c>
       <c r="T24" t="n">
-        <v>1865.871540558192</v>
+        <v>1541.629116315768</v>
       </c>
       <c r="U24" t="n">
-        <v>1785.911104741727</v>
+        <v>1461.668680499303</v>
       </c>
       <c r="V24" t="n">
         <v>1367.213461113929</v>
       </c>
       <c r="W24" t="n">
-        <v>930.4729127201629</v>
+        <v>930.4729127201631</v>
       </c>
       <c r="X24" t="n">
-        <v>506.3691355025996</v>
+        <v>830.6115597450241</v>
       </c>
       <c r="Y24" t="n">
-        <v>232.5124582880063</v>
+        <v>427.1859104863025</v>
       </c>
     </row>
     <row r="25">
@@ -6117,22 +6117,22 @@
         <v>686.6904483778065</v>
       </c>
       <c r="C25" t="n">
-        <v>734.4824541962423</v>
+        <v>723.3789473147295</v>
       </c>
       <c r="D25" t="n">
-        <v>769.5915983212424</v>
+        <v>758.4880914397296</v>
       </c>
       <c r="E25" t="n">
-        <v>809.2105025326554</v>
+        <v>798.1069956511426</v>
       </c>
       <c r="F25" t="n">
-        <v>855.3614751245908</v>
+        <v>844.257968243078</v>
       </c>
       <c r="G25" t="n">
-        <v>931.1828770770499</v>
+        <v>920.0793701955371</v>
       </c>
       <c r="H25" t="n">
-        <v>1028.044822892185</v>
+        <v>1016.941316010672</v>
       </c>
       <c r="I25" t="n">
         <v>1178.654719536919</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>601.7035838793097</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C26" t="n">
-        <v>471.8996675499188</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D26" t="n">
-        <v>380.6479950854241</v>
+        <v>376.4475910450201</v>
       </c>
       <c r="E26" t="n">
-        <v>295.432551038082</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F26" t="n">
-        <v>209.6854513330196</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G26" t="n">
-        <v>126.5032926349016</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H26" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="I26" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="J26" t="n">
-        <v>561.6952612788618</v>
+        <v>358.796970190582</v>
       </c>
       <c r="K26" t="n">
-        <v>1207.175261278862</v>
+        <v>1002.296970190582</v>
       </c>
       <c r="L26" t="n">
-        <v>1653.796970190582</v>
+        <v>1645.796970190582</v>
       </c>
       <c r="M26" t="n">
-        <v>1653.796970190582</v>
+        <v>1645.796970190582</v>
       </c>
       <c r="N26" t="n">
-        <v>1653.796970190582</v>
+        <v>1645.796970190582</v>
       </c>
       <c r="O26" t="n">
-        <v>1818.950481322281</v>
+        <v>1810.950481322281</v>
       </c>
       <c r="P26" t="n">
-        <v>2018.976374796579</v>
+        <v>2010.976374796579</v>
       </c>
       <c r="Q26" t="n">
-        <v>2608</v>
+        <v>2600</v>
       </c>
       <c r="R26" t="n">
-        <v>2608</v>
+        <v>2594.677071794846</v>
       </c>
       <c r="S26" t="n">
-        <v>2463.772369967706</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T26" t="n">
-        <v>2200.624607092805</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U26" t="n">
-        <v>1868.191542714482</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V26" t="n">
-        <v>1555.21071022274</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W26" t="n">
-        <v>1233.621340545016</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X26" t="n">
-        <v>958.58918553424</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y26" t="n">
-        <v>765.3392535314052</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1144.311491978585</v>
+        <v>1335.794641146578</v>
       </c>
       <c r="C27" t="n">
-        <v>779.56410566998</v>
+        <v>1295.289679080397</v>
       </c>
       <c r="D27" t="n">
-        <v>751.3442199147248</v>
+        <v>1268.079894335243</v>
       </c>
       <c r="E27" t="n">
-        <v>728.4431116097626</v>
+        <v>921.9464627979576</v>
       </c>
       <c r="F27" t="n">
-        <v>385.3762001573617</v>
+        <v>708.4485233896851</v>
       </c>
       <c r="G27" t="n">
-        <v>57.10680047418182</v>
+        <v>380.1791237065051</v>
       </c>
       <c r="H27" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="I27" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="J27" t="n">
-        <v>246.5312041375631</v>
+        <v>246.3712041375631</v>
       </c>
       <c r="K27" t="n">
-        <v>556.0739306093051</v>
+        <v>555.913930609305</v>
       </c>
       <c r="L27" t="n">
-        <v>989.2496988082788</v>
+        <v>989.0896988082787</v>
       </c>
       <c r="M27" t="n">
-        <v>1264.172740551138</v>
+        <v>1264.012740551138</v>
       </c>
       <c r="N27" t="n">
-        <v>1591.29362421531</v>
+        <v>1591.13362421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2007.662354200916</v>
+        <v>2007.502354200916</v>
       </c>
       <c r="P27" t="n">
-        <v>2262.511670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2262.511670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="R27" t="n">
-        <v>1897.603583969818</v>
+        <v>2081.005925057003</v>
       </c>
       <c r="S27" t="n">
-        <v>1763.683877506612</v>
+        <v>1948.096319603899</v>
       </c>
       <c r="T27" t="n">
-        <v>1680.528997450805</v>
+        <v>1865.951540558192</v>
       </c>
       <c r="U27" t="n">
-        <v>1599.558460624239</v>
+        <v>1785.991104741727</v>
       </c>
       <c r="V27" t="n">
-        <v>1504.093140228764</v>
+        <v>1691.535885356353</v>
       </c>
       <c r="W27" t="n">
-        <v>1390.584915067321</v>
+        <v>1579.037761205011</v>
       </c>
       <c r="X27" t="n">
-        <v>1289.713461082081</v>
+        <v>1479.176408229872</v>
       </c>
       <c r="Y27" t="n">
-        <v>1209.520135055683</v>
+        <v>1399.993183213575</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>680.0004483778066</v>
+        <v>675.6669414962937</v>
       </c>
       <c r="C28" t="n">
-        <v>726.8024541962424</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D28" t="n">
-        <v>760.9215983212424</v>
+        <v>758.5680914397295</v>
       </c>
       <c r="E28" t="n">
-        <v>799.5505025326554</v>
+        <v>798.1869956511425</v>
       </c>
       <c r="F28" t="n">
-        <v>844.7114751245908</v>
+        <v>844.337968243078</v>
       </c>
       <c r="G28" t="n">
-        <v>919.5428770770499</v>
+        <v>920.159370195537</v>
       </c>
       <c r="H28" t="n">
-        <v>1015.414822892185</v>
+        <v>1017.021316010672</v>
       </c>
       <c r="I28" t="n">
-        <v>1176.138226418432</v>
+        <v>1178.734719536919</v>
       </c>
       <c r="J28" t="n">
-        <v>1502.197876906949</v>
+        <v>1505.784370025436</v>
       </c>
       <c r="K28" t="n">
-        <v>1605.956901007752</v>
+        <v>1610.533394126239</v>
       </c>
       <c r="L28" t="n">
-        <v>1605.956901007752</v>
+        <v>1601.732180057278</v>
       </c>
       <c r="M28" t="n">
-        <v>1506.239285611914</v>
+        <v>1500.018679551308</v>
       </c>
       <c r="N28" t="n">
-        <v>1350.075357948844</v>
+        <v>1344.864852898339</v>
       </c>
       <c r="O28" t="n">
-        <v>1116.503915511025</v>
+        <v>1112.303511470621</v>
       </c>
       <c r="P28" t="n">
-        <v>822.449904300147</v>
+        <v>819.2596012698439</v>
       </c>
       <c r="Q28" t="n">
-        <v>465.8950897288359</v>
+        <v>463.7148877086339</v>
       </c>
       <c r="R28" t="n">
-        <v>83.85121148988544</v>
+        <v>82.68111047978442</v>
       </c>
       <c r="S28" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="T28" t="n">
-        <v>163.7054332571655</v>
+        <v>153.4319263756526</v>
       </c>
       <c r="U28" t="n">
-        <v>331.0907078626653</v>
+        <v>321.8072009811523</v>
       </c>
       <c r="V28" t="n">
-        <v>450.7121007486112</v>
+        <v>442.4185938670983</v>
       </c>
       <c r="W28" t="n">
-        <v>543.4030190082887</v>
+        <v>536.0995121267757</v>
       </c>
       <c r="X28" t="n">
-        <v>615.2338100324822</v>
+        <v>608.9203031509693</v>
       </c>
       <c r="Y28" t="n">
-        <v>647.4431107115145</v>
+        <v>642.1196038300016</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>601.7035838793097</v>
+        <v>601.7843919601175</v>
       </c>
       <c r="C29" t="n">
-        <v>470.9211816136593</v>
+        <v>472.0120907045681</v>
       </c>
       <c r="D29" t="n">
-        <v>379.6695091491645</v>
+        <v>381.7705192501743</v>
       </c>
       <c r="E29" t="n">
-        <v>294.4540651018224</v>
+        <v>297.5651762129333</v>
       </c>
       <c r="F29" t="n">
-        <v>209.6854513330196</v>
+        <v>212.8281775179718</v>
       </c>
       <c r="G29" t="n">
-        <v>126.5032926349016</v>
+        <v>130.6561198299548</v>
       </c>
       <c r="H29" t="n">
-        <v>52.16</v>
+        <v>57.32292820515428</v>
       </c>
       <c r="I29" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="J29" t="n">
-        <v>561.6952612788618</v>
+        <v>561.5352612788618</v>
       </c>
       <c r="K29" t="n">
-        <v>951.8605953940029</v>
+        <v>738.7256105250929</v>
       </c>
       <c r="L29" t="n">
-        <v>1597.340595394003</v>
+        <v>958.545907007505</v>
       </c>
       <c r="M29" t="n">
-        <v>1597.340595394003</v>
+        <v>958.5459070075051</v>
       </c>
       <c r="N29" t="n">
-        <v>2242.820595394003</v>
+        <v>1602.045907007505</v>
       </c>
       <c r="O29" t="n">
-        <v>2407.974106525702</v>
+        <v>1810.950481322281</v>
       </c>
       <c r="P29" t="n">
-        <v>2608</v>
+        <v>2010.976374796579</v>
       </c>
       <c r="Q29" t="n">
-        <v>2608</v>
+        <v>2600</v>
       </c>
       <c r="R29" t="n">
-        <v>2608</v>
+        <v>2600</v>
       </c>
       <c r="S29" t="n">
-        <v>2463.772369967706</v>
+        <v>2456.782470977807</v>
       </c>
       <c r="T29" t="n">
-        <v>2200.624607092805</v>
+        <v>2194.644809113007</v>
       </c>
       <c r="U29" t="n">
-        <v>1868.191542714482</v>
+        <v>1863.221845744784</v>
       </c>
       <c r="V29" t="n">
-        <v>1555.21071022274</v>
+        <v>1551.251114263144</v>
       </c>
       <c r="W29" t="n">
-        <v>1233.621340545016</v>
+        <v>1230.67184559552</v>
       </c>
       <c r="X29" t="n">
-        <v>958.58918553424</v>
+        <v>956.6497915948457</v>
       </c>
       <c r="Y29" t="n">
-        <v>765.3392535314052</v>
+        <v>764.4099606021121</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1326.86373205567</v>
+        <v>687.3097926617302</v>
       </c>
       <c r="C30" t="n">
-        <v>1285.348668979388</v>
+        <v>646.8048305955491</v>
       </c>
       <c r="D30" t="n">
-        <v>933.8964599918095</v>
+        <v>619.595045850395</v>
       </c>
       <c r="E30" t="n">
-        <v>910.9953516868472</v>
+        <v>597.7040385555338</v>
       </c>
       <c r="F30" t="n">
-        <v>567.9284402344463</v>
+        <v>254.6371271031329</v>
       </c>
       <c r="G30" t="n">
-        <v>562.8913637835896</v>
+        <v>250.6101516623772</v>
       </c>
       <c r="H30" t="n">
-        <v>245.2979541117109</v>
+        <v>245.1379541117109</v>
       </c>
       <c r="I30" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="J30" t="n">
-        <v>246.5312041375631</v>
+        <v>246.3712041375631</v>
       </c>
       <c r="K30" t="n">
-        <v>556.0739306093051</v>
+        <v>555.913930609305</v>
       </c>
       <c r="L30" t="n">
-        <v>989.2496988082788</v>
+        <v>989.0896988082787</v>
       </c>
       <c r="M30" t="n">
-        <v>1264.172740551138</v>
+        <v>1264.012740551138</v>
       </c>
       <c r="N30" t="n">
-        <v>1591.29362421531</v>
+        <v>1591.13362421531</v>
       </c>
       <c r="O30" t="n">
-        <v>2007.662354200916</v>
+        <v>2007.502354200916</v>
       </c>
       <c r="P30" t="n">
-        <v>2262.511670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2262.511670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="R30" t="n">
-        <v>2080.155824046903</v>
+        <v>2081.005925057003</v>
       </c>
       <c r="S30" t="n">
-        <v>1946.236117583697</v>
+        <v>1948.096319603899</v>
       </c>
       <c r="T30" t="n">
-        <v>1863.081237527889</v>
+        <v>1541.709116315768</v>
       </c>
       <c r="U30" t="n">
-        <v>1782.110700701324</v>
+        <v>1461.748680499303</v>
       </c>
       <c r="V30" t="n">
-        <v>1686.645380305849</v>
+        <v>1367.293461113929</v>
       </c>
       <c r="W30" t="n">
-        <v>1573.137155144406</v>
+        <v>1254.795336962587</v>
       </c>
       <c r="X30" t="n">
-        <v>1472.265701159166</v>
+        <v>1154.933983987448</v>
       </c>
       <c r="Y30" t="n">
-        <v>1392.072375132768</v>
+        <v>751.5083347287267</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>680.0004483778066</v>
+        <v>675.6669414962937</v>
       </c>
       <c r="C31" t="n">
-        <v>726.8024541962424</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D31" t="n">
-        <v>760.9215983212424</v>
+        <v>758.5680914397295</v>
       </c>
       <c r="E31" t="n">
-        <v>799.5505025326554</v>
+        <v>798.1869956511425</v>
       </c>
       <c r="F31" t="n">
-        <v>844.7114751245908</v>
+        <v>844.337968243078</v>
       </c>
       <c r="G31" t="n">
-        <v>919.5428770770499</v>
+        <v>920.159370195537</v>
       </c>
       <c r="H31" t="n">
-        <v>1015.414822892185</v>
+        <v>1017.021316010672</v>
       </c>
       <c r="I31" t="n">
-        <v>1176.138226418432</v>
+        <v>1178.734719536919</v>
       </c>
       <c r="J31" t="n">
-        <v>1502.197876906949</v>
+        <v>1505.784370025436</v>
       </c>
       <c r="K31" t="n">
-        <v>1605.956901007752</v>
+        <v>1610.533394126239</v>
       </c>
       <c r="L31" t="n">
-        <v>1605.956901007752</v>
+        <v>1601.732180057278</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.239285611914</v>
+        <v>1500.018679551308</v>
       </c>
       <c r="N31" t="n">
-        <v>1350.075357948844</v>
+        <v>1344.864852898339</v>
       </c>
       <c r="O31" t="n">
-        <v>1116.503915511025</v>
+        <v>1112.303511470621</v>
       </c>
       <c r="P31" t="n">
-        <v>822.449904300147</v>
+        <v>819.2596012698439</v>
       </c>
       <c r="Q31" t="n">
-        <v>465.8950897288359</v>
+        <v>463.7148877086339</v>
       </c>
       <c r="R31" t="n">
-        <v>83.85121148988544</v>
+        <v>82.68111047978442</v>
       </c>
       <c r="S31" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="T31" t="n">
-        <v>163.7054332571655</v>
+        <v>153.4319263756526</v>
       </c>
       <c r="U31" t="n">
-        <v>331.0907078626653</v>
+        <v>321.8072009811523</v>
       </c>
       <c r="V31" t="n">
-        <v>450.7121007486112</v>
+        <v>442.4185938670983</v>
       </c>
       <c r="W31" t="n">
-        <v>543.4030190082887</v>
+        <v>536.0995121267757</v>
       </c>
       <c r="X31" t="n">
-        <v>615.2338100324822</v>
+        <v>608.9203031509693</v>
       </c>
       <c r="Y31" t="n">
-        <v>647.4431107115145</v>
+        <v>642.1196038300016</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>601.7035838793097</v>
+        <v>596.4614637549632</v>
       </c>
       <c r="C32" t="n">
-        <v>470.9211816136593</v>
+        <v>466.6891624994138</v>
       </c>
       <c r="D32" t="n">
-        <v>379.6695091491645</v>
+        <v>376.4475910450201</v>
       </c>
       <c r="E32" t="n">
-        <v>294.4540651018224</v>
+        <v>292.242248007779</v>
       </c>
       <c r="F32" t="n">
-        <v>208.70696539676</v>
+        <v>207.5052493128175</v>
       </c>
       <c r="G32" t="n">
-        <v>126.5032926349016</v>
+        <v>125.3331916248005</v>
       </c>
       <c r="H32" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="I32" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="J32" t="n">
-        <v>135.6935720585666</v>
+        <v>304.3205953940029</v>
       </c>
       <c r="K32" t="n">
-        <v>671.5600000000001</v>
+        <v>947.8205953940028</v>
       </c>
       <c r="L32" t="n">
-        <v>1317.04</v>
+        <v>1591.320595394003</v>
       </c>
       <c r="M32" t="n">
-        <v>1317.04</v>
+        <v>1591.320595394003</v>
       </c>
       <c r="N32" t="n">
-        <v>1317.04</v>
+        <v>2234.820595394003</v>
       </c>
       <c r="O32" t="n">
-        <v>1962.52</v>
+        <v>2399.974106525702</v>
       </c>
       <c r="P32" t="n">
-        <v>2608</v>
+        <v>2600</v>
       </c>
       <c r="Q32" t="n">
-        <v>2608</v>
+        <v>2600</v>
       </c>
       <c r="R32" t="n">
-        <v>2608</v>
+        <v>2600</v>
       </c>
       <c r="S32" t="n">
-        <v>2463.772369967706</v>
+        <v>2451.459542772653</v>
       </c>
       <c r="T32" t="n">
-        <v>2200.624607092805</v>
+        <v>2189.321880907853</v>
       </c>
       <c r="U32" t="n">
-        <v>1868.191542714482</v>
+        <v>1857.89891753963</v>
       </c>
       <c r="V32" t="n">
-        <v>1555.21071022274</v>
+        <v>1545.92818605799</v>
       </c>
       <c r="W32" t="n">
-        <v>1233.621340545016</v>
+        <v>1225.348917390366</v>
       </c>
       <c r="X32" t="n">
-        <v>958.58918553424</v>
+        <v>951.3268633896914</v>
       </c>
       <c r="Y32" t="n">
-        <v>765.3392535314052</v>
+        <v>759.0870323969577</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1326.86373205567</v>
+        <v>168.3939162210096</v>
       </c>
       <c r="C33" t="n">
-        <v>962.1163457470645</v>
+        <v>127.8889541548285</v>
       </c>
       <c r="D33" t="n">
-        <v>933.8964599918094</v>
+        <v>100.6791694096743</v>
       </c>
       <c r="E33" t="n">
-        <v>587.7630284545239</v>
+        <v>78.7881621148131</v>
       </c>
       <c r="F33" t="n">
-        <v>244.696117002123</v>
+        <v>59.96367490483647</v>
       </c>
       <c r="G33" t="n">
-        <v>239.6590405512663</v>
+        <v>55.93669946408081</v>
       </c>
       <c r="H33" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="I33" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="J33" t="n">
-        <v>246.5312041375631</v>
+        <v>246.3712041375631</v>
       </c>
       <c r="K33" t="n">
-        <v>556.0739306093051</v>
+        <v>555.913930609305</v>
       </c>
       <c r="L33" t="n">
-        <v>989.2496988082788</v>
+        <v>989.0896988082787</v>
       </c>
       <c r="M33" t="n">
-        <v>1264.172740551138</v>
+        <v>1264.012740551138</v>
       </c>
       <c r="N33" t="n">
-        <v>1591.29362421531</v>
+        <v>1591.13362421531</v>
       </c>
       <c r="O33" t="n">
-        <v>2007.662354200916</v>
+        <v>2007.502354200916</v>
       </c>
       <c r="P33" t="n">
-        <v>2262.511670368536</v>
+        <v>2262.351670368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2262.511670368536</v>
+        <v>2184.592931092847</v>
       </c>
       <c r="R33" t="n">
-        <v>2080.155824046903</v>
+        <v>2003.247185781314</v>
       </c>
       <c r="S33" t="n">
-        <v>1946.236117583697</v>
+        <v>1546.095156085785</v>
       </c>
       <c r="T33" t="n">
-        <v>1863.081237527889</v>
+        <v>1139.707952797654</v>
       </c>
       <c r="U33" t="n">
-        <v>1782.110700701324</v>
+        <v>1059.74751698119</v>
       </c>
       <c r="V33" t="n">
-        <v>1686.645380305849</v>
+        <v>641.0498733533914</v>
       </c>
       <c r="W33" t="n">
-        <v>1573.137155144406</v>
+        <v>528.5517492020495</v>
       </c>
       <c r="X33" t="n">
-        <v>1472.265701159166</v>
+        <v>428.6903962269105</v>
       </c>
       <c r="Y33" t="n">
-        <v>1392.072375132768</v>
+        <v>232.5924582880062</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>680.0004483778066</v>
+        <v>675.6669414962937</v>
       </c>
       <c r="C34" t="n">
-        <v>726.8024541962424</v>
+        <v>723.4589473147295</v>
       </c>
       <c r="D34" t="n">
-        <v>760.9215983212424</v>
+        <v>758.5680914397295</v>
       </c>
       <c r="E34" t="n">
-        <v>799.5505025326554</v>
+        <v>798.1869956511425</v>
       </c>
       <c r="F34" t="n">
-        <v>844.7114751245908</v>
+        <v>844.337968243078</v>
       </c>
       <c r="G34" t="n">
-        <v>919.5428770770499</v>
+        <v>920.159370195537</v>
       </c>
       <c r="H34" t="n">
-        <v>1015.414822892185</v>
+        <v>1017.021316010672</v>
       </c>
       <c r="I34" t="n">
-        <v>1176.138226418432</v>
+        <v>1178.734719536919</v>
       </c>
       <c r="J34" t="n">
-        <v>1502.197876906949</v>
+        <v>1505.784370025436</v>
       </c>
       <c r="K34" t="n">
-        <v>1605.956901007752</v>
+        <v>1610.533394126239</v>
       </c>
       <c r="L34" t="n">
-        <v>1605.956901007752</v>
+        <v>1601.732180057278</v>
       </c>
       <c r="M34" t="n">
-        <v>1506.239285611914</v>
+        <v>1500.018679551308</v>
       </c>
       <c r="N34" t="n">
-        <v>1350.075357948844</v>
+        <v>1344.864852898339</v>
       </c>
       <c r="O34" t="n">
-        <v>1116.503915511025</v>
+        <v>1112.303511470621</v>
       </c>
       <c r="P34" t="n">
-        <v>822.449904300147</v>
+        <v>819.2596012698439</v>
       </c>
       <c r="Q34" t="n">
-        <v>465.8950897288359</v>
+        <v>463.7148877086339</v>
       </c>
       <c r="R34" t="n">
-        <v>83.85121148988544</v>
+        <v>82.68111047978442</v>
       </c>
       <c r="S34" t="n">
-        <v>52.16</v>
+        <v>52</v>
       </c>
       <c r="T34" t="n">
-        <v>163.7054332571655</v>
+        <v>153.4319263756526</v>
       </c>
       <c r="U34" t="n">
-        <v>331.0907078626653</v>
+        <v>321.8072009811523</v>
       </c>
       <c r="V34" t="n">
-        <v>450.7121007486112</v>
+        <v>442.4185938670983</v>
       </c>
       <c r="W34" t="n">
-        <v>543.4030190082887</v>
+        <v>536.0995121267757</v>
       </c>
       <c r="X34" t="n">
-        <v>615.2338100324822</v>
+        <v>608.9203031509693</v>
       </c>
       <c r="Y34" t="n">
-        <v>647.4431107115145</v>
+        <v>642.1196038300016</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>443.9669183004178</v>
+        <v>443.7269183004178</v>
       </c>
       <c r="C35" t="n">
-        <v>338.4370412872926</v>
+        <v>338.1970412872926</v>
       </c>
       <c r="D35" t="n">
-        <v>272.4378940753231</v>
+        <v>272.1978940753231</v>
       </c>
       <c r="E35" t="n">
-        <v>212.4749752805063</v>
+        <v>212.2349752805063</v>
       </c>
       <c r="F35" t="n">
-        <v>151.980400827969</v>
+        <v>151.740400827969</v>
       </c>
       <c r="G35" t="n">
-        <v>94.05076738237631</v>
+        <v>93.8107673823763</v>
       </c>
       <c r="H35" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>128.4935720585666</v>
+        <v>128.2535720585666</v>
       </c>
       <c r="K35" t="n">
-        <v>684.8735720585665</v>
+        <v>681.6635720585666</v>
       </c>
       <c r="L35" t="n">
-        <v>1241.253572058567</v>
+        <v>1235.073572058566</v>
       </c>
       <c r="M35" t="n">
-        <v>1326.440595394003</v>
+        <v>1235.073572058566</v>
       </c>
       <c r="N35" t="n">
-        <v>1882.820595394003</v>
+        <v>1235.073572058566</v>
       </c>
       <c r="O35" t="n">
-        <v>2047.974106525702</v>
+        <v>1482.564106525693</v>
       </c>
       <c r="P35" t="n">
-        <v>2248</v>
+        <v>1682.589999999991</v>
       </c>
       <c r="Q35" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2248</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="S35" t="n">
-        <v>2129.268027621137</v>
+        <v>2117.024895220275</v>
       </c>
       <c r="T35" t="n">
-        <v>1891.372789998762</v>
+        <v>1879.129657597899</v>
       </c>
       <c r="U35" t="n">
-        <v>1584.192250872963</v>
+        <v>1571.949118472101</v>
       </c>
       <c r="V35" t="n">
-        <v>1296.463943633747</v>
+        <v>1284.220811232885</v>
       </c>
       <c r="W35" t="n">
-        <v>1000.127099208548</v>
+        <v>987.8839668076851</v>
       </c>
       <c r="X35" t="n">
-        <v>750.3474694502975</v>
+        <v>738.1043370494349</v>
       </c>
       <c r="Y35" t="n">
-        <v>582.350062699988</v>
+        <v>582.110062699988</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>761.1595952961839</v>
+        <v>752.8963527145188</v>
       </c>
       <c r="C36" t="n">
-        <v>396.4122089875784</v>
+        <v>388.1489664059134</v>
       </c>
       <c r="D36" t="n">
-        <v>44.96</v>
+        <v>385.1816059031835</v>
       </c>
       <c r="E36" t="n">
-        <v>44.96</v>
+        <v>237.8579541117109</v>
       </c>
       <c r="F36" t="n">
-        <v>44.96</v>
+        <v>237.8579541117109</v>
       </c>
       <c r="G36" t="n">
-        <v>44.96</v>
+        <v>237.8579541117109</v>
       </c>
       <c r="H36" t="n">
-        <v>44.96</v>
+        <v>237.8579541117109</v>
       </c>
       <c r="I36" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="J36" t="n">
-        <v>239.3312041375631</v>
+        <v>239.0912041375631</v>
       </c>
       <c r="K36" t="n">
-        <v>548.873930609305</v>
+        <v>548.633930609305</v>
       </c>
       <c r="L36" t="n">
-        <v>974.7380284397429</v>
+        <v>962.7380284397866</v>
       </c>
       <c r="M36" t="n">
-        <v>1249.661070182602</v>
+        <v>1237.661070182646</v>
       </c>
       <c r="N36" t="n">
-        <v>1576.781953846774</v>
+        <v>1564.781953846818</v>
       </c>
       <c r="O36" t="n">
-        <v>1993.15068383238</v>
+        <v>1981.150683832424</v>
       </c>
       <c r="P36" t="n">
-        <v>2248</v>
+        <v>2236.000000000044</v>
       </c>
       <c r="Q36" t="n">
-        <v>2170.241260724311</v>
+        <v>2158.241260724355</v>
       </c>
       <c r="R36" t="n">
-        <v>2013.137939655203</v>
+        <v>2001.137939655247</v>
       </c>
       <c r="S36" t="n">
-        <v>1904.470758444523</v>
+        <v>1892.470758444566</v>
       </c>
       <c r="T36" t="n">
-        <v>1842.831646222949</v>
+        <v>1834.568403641284</v>
       </c>
       <c r="U36" t="n">
-        <v>1787.113634648908</v>
+        <v>1778.850392067243</v>
       </c>
       <c r="V36" t="n">
-        <v>1716.900839505959</v>
+        <v>1708.637596924294</v>
       </c>
       <c r="W36" t="n">
-        <v>1628.645139597041</v>
+        <v>1620.381897015376</v>
       </c>
       <c r="X36" t="n">
-        <v>1204.541362379478</v>
+        <v>1196.278119797813</v>
       </c>
       <c r="Y36" t="n">
-        <v>1149.600561605605</v>
+        <v>792.8524705390911</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>846.0504483778067</v>
+        <v>581.3191411954476</v>
       </c>
       <c r="C37" t="n">
-        <v>846.0504483778067</v>
+        <v>581.3191411954476</v>
       </c>
       <c r="D37" t="n">
-        <v>904.9195925028067</v>
+        <v>640.1882853204477</v>
       </c>
       <c r="E37" t="n">
-        <v>968.2984967142197</v>
+        <v>640.1882853204477</v>
       </c>
       <c r="F37" t="n">
-        <v>1038.209469306155</v>
+        <v>710.0992579123831</v>
       </c>
       <c r="G37" t="n">
-        <v>1137.790871258614</v>
+        <v>809.6806598648421</v>
       </c>
       <c r="H37" t="n">
-        <v>1230.262156345545</v>
+        <v>930.3026056799774</v>
       </c>
       <c r="I37" t="n">
-        <v>1415.735559871792</v>
+        <v>930.3026056799774</v>
       </c>
       <c r="J37" t="n">
-        <v>1424.995210360309</v>
+        <v>1281.112256168494</v>
       </c>
       <c r="K37" t="n">
-        <v>1424.995210360309</v>
+        <v>1409.621280269297</v>
       </c>
       <c r="L37" t="n">
-        <v>1424.995210360309</v>
+        <v>1424.755210360309</v>
       </c>
       <c r="M37" t="n">
-        <v>1347.524134096763</v>
+        <v>1347.284134096763</v>
       </c>
       <c r="N37" t="n">
-        <v>1216.612731686218</v>
+        <v>1216.372731686218</v>
       </c>
       <c r="O37" t="n">
-        <v>1008.293814500924</v>
+        <v>1008.053814500924</v>
       </c>
       <c r="P37" t="n">
-        <v>739.4923285425713</v>
+        <v>739.2523285425713</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.1900392237854</v>
+        <v>407.9500392237854</v>
       </c>
       <c r="R37" t="n">
-        <v>51.39868623736019</v>
+        <v>51.15868623736019</v>
       </c>
       <c r="S37" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>181.2554332571655</v>
+        <v>181.0154332571655</v>
       </c>
       <c r="U37" t="n">
-        <v>373.3907078626653</v>
+        <v>349.6115845904458</v>
       </c>
       <c r="V37" t="n">
-        <v>517.7621007486113</v>
+        <v>349.6115845904458</v>
       </c>
       <c r="W37" t="n">
-        <v>635.2030190082887</v>
+        <v>467.0525028501232</v>
       </c>
       <c r="X37" t="n">
-        <v>731.7838100324823</v>
+        <v>467.0525028501232</v>
       </c>
       <c r="Y37" t="n">
-        <v>788.7431107115145</v>
+        <v>524.0118035291555</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>443.9669183004178</v>
+        <v>431.7237858995115</v>
       </c>
       <c r="C38" t="n">
-        <v>338.4370412872926</v>
+        <v>326.1939088863863</v>
       </c>
       <c r="D38" t="n">
-        <v>272.4378940753231</v>
+        <v>260.1947616744168</v>
       </c>
       <c r="E38" t="n">
-        <v>212.4749752805062</v>
+        <v>200.2318428796</v>
       </c>
       <c r="F38" t="n">
-        <v>151.980400827969</v>
+        <v>139.7372684270628</v>
       </c>
       <c r="G38" t="n">
-        <v>94.05076738237628</v>
+        <v>93.81076738237627</v>
       </c>
       <c r="H38" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="I38" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>554.4952612788618</v>
+        <v>210.5905953939797</v>
       </c>
       <c r="K38" t="n">
-        <v>1110.875261278862</v>
+        <v>764.0005953939797</v>
       </c>
       <c r="L38" t="n">
-        <v>1667.255261278862</v>
+        <v>1317.41059539398</v>
       </c>
       <c r="M38" t="n">
-        <v>1882.820595394003</v>
+        <v>1870.820595394003</v>
       </c>
       <c r="N38" t="n">
-        <v>1882.820595394003</v>
+        <v>1870.820595394003</v>
       </c>
       <c r="O38" t="n">
-        <v>2047.974106525702</v>
+        <v>2035.974106525702</v>
       </c>
       <c r="P38" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2129.268027621137</v>
+        <v>2117.024895220231</v>
       </c>
       <c r="T38" t="n">
-        <v>1891.372789998762</v>
+        <v>1879.129657597855</v>
       </c>
       <c r="U38" t="n">
-        <v>1584.192250872963</v>
+        <v>1571.949118472057</v>
       </c>
       <c r="V38" t="n">
-        <v>1296.463943633747</v>
+        <v>1284.220811232841</v>
       </c>
       <c r="W38" t="n">
-        <v>1000.127099208548</v>
+        <v>987.8839668076414</v>
       </c>
       <c r="X38" t="n">
-        <v>750.3474694502975</v>
+        <v>738.1043370493912</v>
       </c>
       <c r="Y38" t="n">
-        <v>582.350062699988</v>
+        <v>570.1069302990818</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>416.4115042296264</v>
+        <v>392.1290220329919</v>
       </c>
       <c r="C39" t="n">
-        <v>400.1489664058695</v>
+        <v>375.866484209235</v>
       </c>
       <c r="D39" t="n">
-        <v>48.69675741829104</v>
+        <v>372.8991237065051</v>
       </c>
       <c r="E39" t="n">
-        <v>48.69675741829104</v>
+        <v>372.8991237065051</v>
       </c>
       <c r="F39" t="n">
-        <v>48.69675741829104</v>
+        <v>372.8991237065051</v>
       </c>
       <c r="G39" t="n">
-        <v>48.69675741829104</v>
+        <v>372.8991237065051</v>
       </c>
       <c r="H39" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="J39" t="n">
-        <v>232.0195337690273</v>
+        <v>239.0912041375631</v>
       </c>
       <c r="K39" t="n">
-        <v>541.5622602407692</v>
+        <v>548.633930609305</v>
       </c>
       <c r="L39" t="n">
-        <v>974.7380284397429</v>
+        <v>981.8096988082788</v>
       </c>
       <c r="M39" t="n">
-        <v>1249.661070182602</v>
+        <v>1256.732740551138</v>
       </c>
       <c r="N39" t="n">
-        <v>1576.781953846774</v>
+        <v>1583.85362421531</v>
       </c>
       <c r="O39" t="n">
-        <v>1993.15068383238</v>
+        <v>2000.222354200916</v>
       </c>
       <c r="P39" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="Q39" t="n">
-        <v>2170.241260724311</v>
+        <v>2158.241260724311</v>
       </c>
       <c r="R39" t="n">
-        <v>2013.137939655203</v>
+        <v>1652.653091170354</v>
       </c>
       <c r="S39" t="n">
-        <v>1904.470758444523</v>
+        <v>1543.985909959674</v>
       </c>
       <c r="T39" t="n">
-        <v>1846.56840364124</v>
+        <v>1137.598706671543</v>
       </c>
       <c r="U39" t="n">
-        <v>1790.850392067199</v>
+        <v>1081.880695097502</v>
       </c>
       <c r="V39" t="n">
-        <v>1372.152748439401</v>
+        <v>1011.667899954553</v>
       </c>
       <c r="W39" t="n">
-        <v>935.412200045635</v>
+        <v>574.9273515607865</v>
       </c>
       <c r="X39" t="n">
-        <v>511.3084228280718</v>
+        <v>499.3084228280718</v>
       </c>
       <c r="Y39" t="n">
-        <v>456.3676220541987</v>
+        <v>432.0851398575642</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>356.0036891831351</v>
+        <v>596.3678361060147</v>
       </c>
       <c r="C40" t="n">
-        <v>356.0036891831351</v>
+        <v>596.3678361060147</v>
       </c>
       <c r="D40" t="n">
-        <v>414.8728333081351</v>
+        <v>655.2369802310147</v>
       </c>
       <c r="E40" t="n">
-        <v>478.2517375195482</v>
+        <v>660.3817302922832</v>
       </c>
       <c r="F40" t="n">
-        <v>548.1627101114836</v>
+        <v>660.3817302922832</v>
       </c>
       <c r="G40" t="n">
-        <v>624.447256338595</v>
+        <v>759.9631322447423</v>
       </c>
       <c r="H40" t="n">
-        <v>745.0692021537303</v>
+        <v>759.9631322447423</v>
       </c>
       <c r="I40" t="n">
-        <v>930.5426056799772</v>
+        <v>945.4365357709892</v>
       </c>
       <c r="J40" t="n">
-        <v>1281.352256168494</v>
+        <v>1296.246186259506</v>
       </c>
       <c r="K40" t="n">
-        <v>1409.861280269297</v>
+        <v>1424.755210360309</v>
       </c>
       <c r="L40" t="n">
-        <v>1424.995210360309</v>
+        <v>1424.755210360309</v>
       </c>
       <c r="M40" t="n">
-        <v>1347.524134096763</v>
+        <v>1347.284134096763</v>
       </c>
       <c r="N40" t="n">
-        <v>1216.612731686218</v>
+        <v>1216.372731686218</v>
       </c>
       <c r="O40" t="n">
-        <v>1008.293814500924</v>
+        <v>1008.053814500924</v>
       </c>
       <c r="P40" t="n">
-        <v>739.4923285425712</v>
+        <v>739.2523285425711</v>
       </c>
       <c r="Q40" t="n">
-        <v>408.1900392237853</v>
+        <v>407.9500392237853</v>
       </c>
       <c r="R40" t="n">
-        <v>51.39868623736021</v>
+        <v>51.15868623736021</v>
       </c>
       <c r="S40" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>181.2554332571655</v>
+        <v>181.0154332571655</v>
       </c>
       <c r="U40" t="n">
-        <v>181.2554332571655</v>
+        <v>181.0154332571655</v>
       </c>
       <c r="V40" t="n">
-        <v>181.2554332571655</v>
+        <v>325.3868261431115</v>
       </c>
       <c r="W40" t="n">
-        <v>298.6963515168429</v>
+        <v>442.8277444027889</v>
       </c>
       <c r="X40" t="n">
-        <v>298.6963515168429</v>
+        <v>539.4085354269824</v>
       </c>
       <c r="Y40" t="n">
-        <v>298.6963515168429</v>
+        <v>596.3678361060147</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>241.7035838793097</v>
+        <v>589.1814637549631</v>
       </c>
       <c r="C41" t="n">
-        <v>110.9211816136593</v>
+        <v>459.4091624994138</v>
       </c>
       <c r="D41" t="n">
-        <v>44.96</v>
+        <v>369.16759104502</v>
       </c>
       <c r="E41" t="n">
-        <v>44.96</v>
+        <v>284.962248007779</v>
       </c>
       <c r="F41" t="n">
-        <v>44.96</v>
+        <v>200.2252493128175</v>
       </c>
       <c r="G41" t="n">
-        <v>44.96</v>
+        <v>118.0531916248005</v>
       </c>
       <c r="H41" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>554.4952612788618</v>
+        <v>128.2535720585666</v>
       </c>
       <c r="K41" t="n">
-        <v>770.060595394003</v>
+        <v>681.6635720585666</v>
       </c>
       <c r="L41" t="n">
-        <v>1326.440595394003</v>
+        <v>1235.073572058566</v>
       </c>
       <c r="M41" t="n">
-        <v>1326.440595394003</v>
+        <v>1235.073572058566</v>
       </c>
       <c r="N41" t="n">
-        <v>1326.440595394003</v>
+        <v>1317.410595393965</v>
       </c>
       <c r="O41" t="n">
-        <v>1491.594106525702</v>
+        <v>1482.564106525664</v>
       </c>
       <c r="P41" t="n">
-        <v>1691.62</v>
+        <v>1682.589999999962</v>
       </c>
       <c r="Q41" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2103.772369967706</v>
+        <v>2092.782470977807</v>
       </c>
       <c r="T41" t="n">
-        <v>1840.624607092805</v>
+        <v>1830.644809113007</v>
       </c>
       <c r="U41" t="n">
-        <v>1508.191542714482</v>
+        <v>1830.644809113007</v>
       </c>
       <c r="V41" t="n">
-        <v>1195.21071022274</v>
+        <v>1518.674077631367</v>
       </c>
       <c r="W41" t="n">
-        <v>873.6213405450155</v>
+        <v>1198.094808963743</v>
       </c>
       <c r="X41" t="n">
-        <v>598.58918553424</v>
+        <v>944.0468633896915</v>
       </c>
       <c r="Y41" t="n">
-        <v>405.3392535314052</v>
+        <v>751.8070323969577</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1007.017122857973</v>
+        <v>809.5987647058582</v>
       </c>
       <c r="C42" t="n">
-        <v>642.2697365493678</v>
+        <v>444.8513783972528</v>
       </c>
       <c r="D42" t="n">
-        <v>614.0498507941127</v>
+        <v>417.6415936520986</v>
       </c>
       <c r="E42" t="n">
-        <v>591.1487424891504</v>
+        <v>395.7505863572374</v>
       </c>
       <c r="F42" t="n">
-        <v>571.3141542690728</v>
+        <v>376.9260991472607</v>
       </c>
       <c r="G42" t="n">
-        <v>566.2770778182161</v>
+        <v>372.8991237065051</v>
       </c>
       <c r="H42" t="n">
-        <v>238.0979541117109</v>
+        <v>44.72</v>
       </c>
       <c r="I42" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="J42" t="n">
-        <v>232.0195337690273</v>
+        <v>239.0912041375631</v>
       </c>
       <c r="K42" t="n">
-        <v>541.5622602407692</v>
+        <v>548.633930609305</v>
       </c>
       <c r="L42" t="n">
-        <v>974.7380284397429</v>
+        <v>981.8096988082788</v>
       </c>
       <c r="M42" t="n">
-        <v>1249.661070182602</v>
+        <v>1237.661070182602</v>
       </c>
       <c r="N42" t="n">
-        <v>1576.781953846774</v>
+        <v>1564.781953846774</v>
       </c>
       <c r="O42" t="n">
-        <v>1993.15068383238</v>
+        <v>1981.15068383238</v>
       </c>
       <c r="P42" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="Q42" t="n">
-        <v>2170.241260724311</v>
+        <v>2236</v>
       </c>
       <c r="R42" t="n">
-        <v>1987.885414402677</v>
+        <v>1879.052472858707</v>
       </c>
       <c r="S42" t="n">
-        <v>1853.965707939472</v>
+        <v>1421.900443163179</v>
       </c>
       <c r="T42" t="n">
-        <v>1770.810827883664</v>
+        <v>1339.755664117472</v>
       </c>
       <c r="U42" t="n">
-        <v>1689.840291057099</v>
+        <v>1259.795228301007</v>
       </c>
       <c r="V42" t="n">
-        <v>1594.374970661624</v>
+        <v>1165.340008915633</v>
       </c>
       <c r="W42" t="n">
-        <v>1480.866745500181</v>
+        <v>1052.841884764291</v>
       </c>
       <c r="X42" t="n">
-        <v>1379.995291514941</v>
+        <v>952.9805317891521</v>
       </c>
       <c r="Y42" t="n">
-        <v>1299.801965488542</v>
+        <v>873.7973067728548</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>672.8004483778067</v>
+        <v>679.4904483778067</v>
       </c>
       <c r="C43" t="n">
-        <v>719.6024541962424</v>
+        <v>727.2824541962425</v>
       </c>
       <c r="D43" t="n">
-        <v>753.7215983212425</v>
+        <v>762.3915983212426</v>
       </c>
       <c r="E43" t="n">
-        <v>792.3505025326555</v>
+        <v>802.0105025326556</v>
       </c>
       <c r="F43" t="n">
-        <v>837.511475124591</v>
+        <v>848.161475124591</v>
       </c>
       <c r="G43" t="n">
-        <v>912.34287707705</v>
+        <v>923.98287707705</v>
       </c>
       <c r="H43" t="n">
-        <v>1008.214822892185</v>
+        <v>1020.844822892185</v>
       </c>
       <c r="I43" t="n">
-        <v>1168.938226418432</v>
+        <v>1182.558226418432</v>
       </c>
       <c r="J43" t="n">
-        <v>1494.997876906949</v>
+        <v>1498.504370025436</v>
       </c>
       <c r="K43" t="n">
-        <v>1598.756901007752</v>
+        <v>1603.253394126239</v>
       </c>
       <c r="L43" t="n">
-        <v>1588.94558592869</v>
+        <v>1594.452180057279</v>
       </c>
       <c r="M43" t="n">
-        <v>1486.221984412619</v>
+        <v>1492.738679551308</v>
       </c>
       <c r="N43" t="n">
-        <v>1342.875357948844</v>
+        <v>1337.584852898339</v>
       </c>
       <c r="O43" t="n">
-        <v>1109.303915511025</v>
+        <v>1105.023511470621</v>
       </c>
       <c r="P43" t="n">
-        <v>815.249904300147</v>
+        <v>811.9796012698439</v>
       </c>
       <c r="Q43" t="n">
-        <v>458.6950897288359</v>
+        <v>456.4348877086338</v>
       </c>
       <c r="R43" t="n">
-        <v>76.65121148988544</v>
+        <v>75.40111047978445</v>
       </c>
       <c r="S43" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>156.5054332571655</v>
+        <v>157.2554332571655</v>
       </c>
       <c r="U43" t="n">
-        <v>323.8907078626653</v>
+        <v>325.6307078626653</v>
       </c>
       <c r="V43" t="n">
-        <v>443.5121007486113</v>
+        <v>446.2421007486113</v>
       </c>
       <c r="W43" t="n">
-        <v>536.2030190082887</v>
+        <v>539.9230190082887</v>
       </c>
       <c r="X43" t="n">
-        <v>608.0338100324823</v>
+        <v>612.7438100324823</v>
       </c>
       <c r="Y43" t="n">
-        <v>640.2431107115145</v>
+        <v>645.9431107115146</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>385.9312139116037</v>
+        <v>431.6429290929216</v>
       </c>
       <c r="C44" t="n">
-        <v>255.1488116459533</v>
+        <v>301.8706278373722</v>
       </c>
       <c r="D44" t="n">
-        <v>163.8971391814586</v>
+        <v>211.6290563829785</v>
       </c>
       <c r="E44" t="n">
-        <v>163.8971391814586</v>
+        <v>211.6290563829785</v>
       </c>
       <c r="F44" t="n">
-        <v>78.15003947639607</v>
+        <v>126.892057688017</v>
       </c>
       <c r="G44" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="H44" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>128.4935720585666</v>
+        <v>554.2552612788618</v>
       </c>
       <c r="K44" t="n">
-        <v>684.8735720585665</v>
+        <v>731.4456105250929</v>
       </c>
       <c r="L44" t="n">
-        <v>1241.253572058567</v>
+        <v>951.265907007505</v>
       </c>
       <c r="M44" t="n">
-        <v>1797.633572058567</v>
+        <v>951.2659070075051</v>
       </c>
       <c r="N44" t="n">
-        <v>1882.820595394003</v>
+        <v>1482.564106525635</v>
       </c>
       <c r="O44" t="n">
-        <v>2047.974106525702</v>
+        <v>2035.974106525702</v>
       </c>
       <c r="P44" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="Q44" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="T44" t="n">
-        <v>1984.852237125099</v>
+        <v>1973.8623381352</v>
       </c>
       <c r="U44" t="n">
-        <v>1652.419172746776</v>
+        <v>1642.439374766978</v>
       </c>
       <c r="V44" t="n">
-        <v>1339.438340255034</v>
+        <v>1330.468643285337</v>
       </c>
       <c r="W44" t="n">
-        <v>1017.84897057731</v>
+        <v>1009.889374617713</v>
       </c>
       <c r="X44" t="n">
-        <v>742.8168155665339</v>
+        <v>735.867320617039</v>
       </c>
       <c r="Y44" t="n">
-        <v>549.5668835636992</v>
+        <v>543.6274896243053</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1234.593322411445</v>
+        <v>809.5987647058581</v>
       </c>
       <c r="C45" t="n">
-        <v>869.8459361028395</v>
+        <v>769.0938026396771</v>
       </c>
       <c r="D45" t="n">
-        <v>518.3937271152611</v>
+        <v>741.8840178945229</v>
       </c>
       <c r="E45" t="n">
-        <v>172.2602955779756</v>
+        <v>395.7505863572374</v>
       </c>
       <c r="F45" t="n">
-        <v>54.9438769250385</v>
+        <v>376.9260991472607</v>
       </c>
       <c r="G45" t="n">
-        <v>49.90680047418184</v>
+        <v>372.8991237065051</v>
       </c>
       <c r="H45" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="I45" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="J45" t="n">
-        <v>232.0195337690273</v>
+        <v>239.0912041375631</v>
       </c>
       <c r="K45" t="n">
-        <v>541.5622602407692</v>
+        <v>548.633930609305</v>
       </c>
       <c r="L45" t="n">
-        <v>974.7380284397429</v>
+        <v>981.8096988082788</v>
       </c>
       <c r="M45" t="n">
-        <v>1249.661070182602</v>
+        <v>1256.732740551138</v>
       </c>
       <c r="N45" t="n">
-        <v>1576.781953846774</v>
+        <v>1564.781953846774</v>
       </c>
       <c r="O45" t="n">
-        <v>1993.15068383238</v>
+        <v>1981.15068383238</v>
       </c>
       <c r="P45" t="n">
-        <v>2248</v>
+        <v>2236</v>
       </c>
       <c r="Q45" t="n">
-        <v>2170.241260724311</v>
+        <v>2236</v>
       </c>
       <c r="R45" t="n">
-        <v>1987.885414402677</v>
+        <v>2054.654254688468</v>
       </c>
       <c r="S45" t="n">
-        <v>1853.965707939472</v>
+        <v>1921.744649235363</v>
       </c>
       <c r="T45" t="n">
-        <v>1770.810827883664</v>
+        <v>1839.599870189656</v>
       </c>
       <c r="U45" t="n">
-        <v>1689.840291057099</v>
+        <v>1759.639434373191</v>
       </c>
       <c r="V45" t="n">
-        <v>1594.374970661624</v>
+        <v>1340.941790745393</v>
       </c>
       <c r="W45" t="n">
-        <v>1480.866745500181</v>
+        <v>1228.443666594051</v>
       </c>
       <c r="X45" t="n">
-        <v>1379.995291514941</v>
+        <v>952.980531789152</v>
       </c>
       <c r="Y45" t="n">
-        <v>1299.801965488542</v>
+        <v>873.7973067728547</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>672.8004483778067</v>
+        <v>668.386941496294</v>
       </c>
       <c r="C46" t="n">
-        <v>719.6024541962424</v>
+        <v>716.1789473147297</v>
       </c>
       <c r="D46" t="n">
-        <v>753.7215983212425</v>
+        <v>751.2880914397298</v>
       </c>
       <c r="E46" t="n">
-        <v>792.3505025326555</v>
+        <v>790.9069956511428</v>
       </c>
       <c r="F46" t="n">
-        <v>837.511475124591</v>
+        <v>837.0579682430782</v>
       </c>
       <c r="G46" t="n">
-        <v>912.34287707705</v>
+        <v>912.8793701955373</v>
       </c>
       <c r="H46" t="n">
-        <v>1008.214822892185</v>
+        <v>1009.741316010673</v>
       </c>
       <c r="I46" t="n">
-        <v>1168.938226418432</v>
+        <v>1171.454719536919</v>
       </c>
       <c r="J46" t="n">
-        <v>1494.997876906949</v>
+        <v>1498.504370025436</v>
       </c>
       <c r="K46" t="n">
-        <v>1598.756901007752</v>
+        <v>1603.253394126239</v>
       </c>
       <c r="L46" t="n">
-        <v>1598.756901007752</v>
+        <v>1594.452180057278</v>
       </c>
       <c r="M46" t="n">
-        <v>1499.039285611914</v>
+        <v>1492.738679551308</v>
       </c>
       <c r="N46" t="n">
-        <v>1342.875357948844</v>
+        <v>1337.584852898339</v>
       </c>
       <c r="O46" t="n">
-        <v>1109.303915511025</v>
+        <v>1105.023511470621</v>
       </c>
       <c r="P46" t="n">
-        <v>815.249904300147</v>
+        <v>811.9796012698439</v>
       </c>
       <c r="Q46" t="n">
-        <v>458.6950897288359</v>
+        <v>456.4348877086338</v>
       </c>
       <c r="R46" t="n">
-        <v>76.65121148988547</v>
+        <v>75.40111047978442</v>
       </c>
       <c r="S46" t="n">
-        <v>44.96</v>
+        <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>156.5054332571655</v>
+        <v>146.1519263756528</v>
       </c>
       <c r="U46" t="n">
-        <v>323.8907078626653</v>
+        <v>314.5272009811526</v>
       </c>
       <c r="V46" t="n">
-        <v>443.5121007486113</v>
+        <v>435.1385938670986</v>
       </c>
       <c r="W46" t="n">
-        <v>536.2030190082887</v>
+        <v>528.819512126776</v>
       </c>
       <c r="X46" t="n">
-        <v>608.0338100324823</v>
+        <v>601.6403031509695</v>
       </c>
       <c r="Y46" t="n">
-        <v>640.2431107115145</v>
+        <v>634.8396038300018</v>
       </c>
     </row>
   </sheetData>
@@ -7964,19 +7964,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K2" t="n">
         <v>321.3286984924623</v>
       </c>
       <c r="L2" t="n">
-        <v>308.6565929648241</v>
+        <v>234.2887077235403</v>
       </c>
       <c r="M2" t="n">
-        <v>845.554996989051</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
-        <v>702.8967675158527</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O2" t="n">
         <v>0.4816735941929551</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.1077446289929</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8438,10 +8438,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>321.3286984924623</v>
+        <v>246.9608132511784</v>
       </c>
       <c r="L8" t="n">
         <v>308.6565929648241</v>
@@ -8453,7 +8453,7 @@
         <v>777.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>300.0130910804115</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -8532,7 +8532,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O9" t="n">
-        <v>382.6817988009025</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P9" t="n">
         <v>219.1507118405495</v>
@@ -8678,19 +8678,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>470.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>426.9592964824121</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>466.7314091191549</v>
+        <v>881.5322832636558</v>
       </c>
       <c r="N11" t="n">
         <v>875.1881540497347</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>482.1782715841426</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -8912,28 +8912,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>263.2741006722111</v>
+        <v>137.3795779927173</v>
       </c>
       <c r="L14" t="n">
-        <v>426.9592964824121</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>297.1990623156842</v>
+        <v>946.1990623156843</v>
       </c>
       <c r="N14" t="n">
         <v>226.1881540497347</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>482.1782715841426</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>446.9536429552543</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,13 +9152,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>470.019849246231</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>166.1869066997265</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>297.1990623156842</v>
+        <v>338.4324594703072</v>
       </c>
       <c r="N17" t="n">
         <v>875.1881540497347</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,10 +9386,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>470.019849246231</v>
+        <v>470.0198492462312</v>
       </c>
       <c r="L20" t="n">
         <v>426.9592964824121</v>
@@ -9398,16 +9398,16 @@
         <v>297.1990623156842</v>
       </c>
       <c r="N20" t="n">
-        <v>226.1881540497347</v>
+        <v>875.1881540497347</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>169.5323468034707</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>409.1063246955536</v>
+        <v>20.87871447823917</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>417.5114925321142</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>946.1990623156843</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N23" t="n">
         <v>875.1881540497347</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>189.2531129907032</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>446.9536429552543</v>
       </c>
       <c r="Q23" t="n">
         <v>20.87871447823917</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>225.5185839717327</v>
       </c>
       <c r="K26" t="n">
-        <v>473.0198492462313</v>
+        <v>471.0198492462312</v>
       </c>
       <c r="L26" t="n">
-        <v>229.0923357871798</v>
+        <v>427.9592964824121</v>
       </c>
       <c r="M26" t="n">
         <v>297.1990623156842</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>215.1262473423332</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>429.959296482412</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>297.1990623156842</v>
       </c>
       <c r="N29" t="n">
-        <v>878.1881540497347</v>
+        <v>876.1881540497347</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>44.19299311421904</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>20.87871447823917</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,25 +10334,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>170.491942763067</v>
       </c>
       <c r="K32" t="n">
-        <v>362.2990693890932</v>
+        <v>471.0198492462312</v>
       </c>
       <c r="L32" t="n">
-        <v>429.959296482412</v>
+        <v>427.959296482412</v>
       </c>
       <c r="M32" t="n">
         <v>297.1990623156842</v>
       </c>
       <c r="N32" t="n">
-        <v>226.1881540497347</v>
+        <v>876.1881540497347</v>
       </c>
       <c r="O32" t="n">
-        <v>485.1782715841426</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>449.9536429552543</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>20.87871447823917</v>
@@ -10574,25 +10574,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>383.0198492462312</v>
+        <v>380.0198492462312</v>
       </c>
       <c r="L35" t="n">
-        <v>339.9592964824121</v>
+        <v>336.9592964824119</v>
       </c>
       <c r="M35" t="n">
-        <v>383.2465606343068</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N35" t="n">
-        <v>788.1881540497347</v>
+        <v>226.1881540497347</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>83.16871043982604</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>20.87871447823917</v>
+        <v>579.878714478248</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10656,7 +10656,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>380.7038108350145</v>
+        <v>368.8250229562707</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
@@ -10808,16 +10808,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>83.16871043981125</v>
       </c>
       <c r="K38" t="n">
-        <v>383.0198492462312</v>
+        <v>380.0198492462312</v>
       </c>
       <c r="L38" t="n">
-        <v>339.9592964824121</v>
+        <v>336.959296482412</v>
       </c>
       <c r="M38" t="n">
-        <v>514.94182404815</v>
+        <v>856.1990623157075</v>
       </c>
       <c r="N38" t="n">
         <v>226.1881540497347</v>
@@ -10887,7 +10887,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>220.0792163030048</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
@@ -10905,7 +10905,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P39" t="n">
-        <v>219.1507118405495</v>
+        <v>199.8863983369781</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>38.76261097869701</v>
+        <v>380.0198492462312</v>
       </c>
       <c r="L41" t="n">
-        <v>339.959296482412</v>
+        <v>336.9592964824119</v>
       </c>
       <c r="M41" t="n">
         <v>297.1990623156842</v>
       </c>
       <c r="N41" t="n">
-        <v>226.1881540497347</v>
+        <v>309.3568644895316</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>582.8787144782391</v>
+        <v>579.8787144782771</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11124,7 +11124,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>220.0792163030048</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
         <v>295.8802408630135</v>
@@ -11133,7 +11133,7 @@
         <v>388.0893364597981</v>
       </c>
       <c r="M42" t="n">
-        <v>471.6948204301074</v>
+        <v>452.4305069265358</v>
       </c>
       <c r="N42" t="n">
         <v>485.4085271713503</v>
@@ -11282,22 +11282,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>383.0198492462312</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>339.9592964824121</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>859.1990623156843</v>
+        <v>297.1990623156842</v>
       </c>
       <c r="N44" t="n">
-        <v>312.2356523683574</v>
+        <v>762.8530020478462</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>392.1782715842097</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -11361,7 +11361,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>220.0792163030048</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
         <v>295.8802408630135</v>
@@ -11373,7 +11373,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>485.4085271713503</v>
+        <v>466.1442136677788</v>
       </c>
       <c r="O45" t="n">
         <v>382.6817988009037</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.06237890435624e-12</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -24411,7 +24411,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9687010768969628</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -24596,10 +24596,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.713201928270976</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.975926259031354</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -24657,7 +24657,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9687010768970055</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -24833,10 +24833,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.713201928270976</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.975926259031354</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9687010768969957</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -25070,10 +25070,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>9.713201928270976</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.975926259031354</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2407010768969684</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25188,7 +25188,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>11.88310107685399</v>
       </c>
     </row>
     <row r="36">
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>11.88310107689716</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -25407,7 +25407,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2407010768969968</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -25599,19 +25599,19 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>25.03758594232707</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>84.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>84.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>82.35033711113681</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>73.59985970855254</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25650,7 +25650,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>328.1087337345404</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>19.77436734235675</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25787,7 +25787,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>12.68912818730217</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>50.1345980295046</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -25839,16 +25839,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>84.36328960686865</v>
+        <v>83.36328960686865</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>49.4921980295047</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>73.59985970855251</v>
+        <v>72.59985970855254</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>142.7853537319712</v>
+        <v>141.7853537319711</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -26018,10 +26018,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>9.713201928270962</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.975926259031155</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8314315.816173083</v>
+        <v>8314403.40043966</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9227087.475844603</v>
+        <v>9227451.754680788</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10139859.13551613</v>
+        <v>10140500.10892192</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11044289.69137581</v>
+        <v>11044013.12854427</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11957324.1547578</v>
+        <v>11956375.70902226</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12849939.32730933</v>
+        <v>12849347.72950025</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13742554.49986086</v>
+        <v>13742319.74997824</v>
       </c>
     </row>
   </sheetData>
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1290861.46634091</v>
+        <v>1290861.466340909</v>
       </c>
       <c r="C2" t="n">
-        <v>1290861.46634091</v>
+        <v>1290861.466340909</v>
       </c>
       <c r="D2" t="n">
         <v>1290861.46634091</v>
@@ -26284,34 +26284,34 @@
         <v>1290861.46634091</v>
       </c>
       <c r="G2" t="n">
+        <v>1290861.466340909</v>
+      </c>
+      <c r="H2" t="n">
         <v>1290861.46634091</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1290861.466340909</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1290861.46634091</v>
       </c>
-      <c r="J2" t="n">
-        <v>1290470.277466639</v>
-      </c>
       <c r="K2" t="n">
-        <v>1290470.277466639</v>
+        <v>1290861.46634091</v>
       </c>
       <c r="L2" t="n">
-        <v>1290470.277466639</v>
+        <v>1290861.46634091</v>
       </c>
       <c r="M2" t="n">
-        <v>1290841.827540046</v>
+        <v>1289891.92412405</v>
       </c>
       <c r="N2" t="n">
-        <v>1290841.827540046</v>
+        <v>1289891.924124046</v>
       </c>
       <c r="O2" t="n">
-        <v>1261973.174986639</v>
+        <v>1262477.684124046</v>
       </c>
       <c r="P2" t="n">
-        <v>1261973.174986638</v>
+        <v>1262477.684124046</v>
       </c>
     </row>
     <row r="3">
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388704</v>
+        <v>388800</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,13 +26354,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85120</v>
+        <v>83968</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>236000</v>
+        <v>237600</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602166.8573620637</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600158.4933044576</v>
+        <v>599959.4017938484</v>
       </c>
       <c r="D4" t="n">
-        <v>598147.4047756541</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>513253.1653847605</v>
+        <v>513056.3660364837</v>
       </c>
       <c r="F4" t="n">
-        <v>511570.4197316588</v>
+        <v>511373.620383382</v>
       </c>
       <c r="G4" t="n">
-        <v>509885.3519526903</v>
+        <v>509688.5526044134</v>
       </c>
       <c r="H4" t="n">
-        <v>508197.9453958012</v>
+        <v>508001.1460475245</v>
       </c>
       <c r="I4" t="n">
-        <v>506508.1831919707</v>
+        <v>506311.3838436939</v>
       </c>
       <c r="J4" t="n">
-        <v>504383.1885319706</v>
+        <v>504545.7862134473</v>
       </c>
       <c r="K4" t="n">
-        <v>502691.7087596816</v>
+        <v>502851.9789492135</v>
       </c>
       <c r="L4" t="n">
-        <v>500997.8257166139</v>
+        <v>501155.7651072775</v>
       </c>
       <c r="M4" t="n">
-        <v>505918.7103673025</v>
+        <v>505559.3102707675</v>
       </c>
       <c r="N4" t="n">
-        <v>504153.7279332092</v>
+        <v>503793.1759878645</v>
       </c>
       <c r="O4" t="n">
-        <v>487150.0016041832</v>
+        <v>487559.923934161</v>
       </c>
       <c r="P4" t="n">
-        <v>485445.6073709899</v>
+        <v>485851.0486089992</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>74075.349</v>
       </c>
       <c r="J5" t="n">
-        <v>74173.67999999999</v>
+        <v>74136.149</v>
       </c>
       <c r="K5" t="n">
-        <v>74173.67999999999</v>
+        <v>74136.149</v>
       </c>
       <c r="L5" t="n">
-        <v>74173.67999999999</v>
+        <v>74136.149</v>
       </c>
       <c r="M5" t="n">
-        <v>70803.405</v>
+        <v>70621.005</v>
       </c>
       <c r="N5" t="n">
-        <v>70803.405</v>
+        <v>70621.005</v>
       </c>
       <c r="O5" t="n">
-        <v>68701.67999999999</v>
+        <v>68603.349</v>
       </c>
       <c r="P5" t="n">
-        <v>68701.67999999999</v>
+        <v>68603.349</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>398009.4089788467</v>
+        <v>398208.5004894549</v>
       </c>
       <c r="C6" t="n">
-        <v>632090.7730364526</v>
+        <v>632289.8645470609</v>
       </c>
       <c r="D6" t="n">
-        <v>634101.8615652557</v>
+        <v>634300.9530758654</v>
       </c>
       <c r="E6" t="n">
-        <v>109107.9519561496</v>
+        <v>109304.7513044262</v>
       </c>
       <c r="F6" t="n">
-        <v>705215.6976092511</v>
+        <v>705412.4969575277</v>
       </c>
       <c r="G6" t="n">
-        <v>706900.7653882196</v>
+        <v>707097.5647364961</v>
       </c>
       <c r="H6" t="n">
-        <v>708588.1719451082</v>
+        <v>708784.9712933853</v>
       </c>
       <c r="I6" t="n">
-        <v>710277.934148939</v>
+        <v>710474.7334972156</v>
       </c>
       <c r="J6" t="n">
-        <v>323209.4089346686</v>
+        <v>323379.5311274626</v>
       </c>
       <c r="K6" t="n">
-        <v>713604.8887069579</v>
+        <v>713873.3383916965</v>
       </c>
       <c r="L6" t="n">
-        <v>715298.7717500257</v>
+        <v>715569.5522336324</v>
       </c>
       <c r="M6" t="n">
-        <v>628999.7121727437</v>
+        <v>629743.6088532823</v>
       </c>
       <c r="N6" t="n">
-        <v>715884.6946068369</v>
+        <v>715477.7431361817</v>
       </c>
       <c r="O6" t="n">
-        <v>470121.4933824562</v>
+        <v>468714.4111898846</v>
       </c>
       <c r="P6" t="n">
-        <v>707825.8876156486</v>
+        <v>708023.2865150467</v>
       </c>
     </row>
   </sheetData>
@@ -26779,13 +26779,13 @@
         <v>321</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M2" t="n">
         <v>345</v>
@@ -26794,10 +26794,10 @@
         <v>345</v>
       </c>
       <c r="O2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3">
@@ -26883,25 +26883,25 @@
         <v>649</v>
       </c>
       <c r="J4" t="n">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="K4" t="n">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="L4" t="n">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M4" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="N4" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="O4" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="P4" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -26996,7 +26996,7 @@
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -27005,13 +27005,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
       </c>
       <c r="O2" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27082,7 +27082,7 @@
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
         <v>275</v>
@@ -27094,25 +27094,25 @@
         <v>-0</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>-0</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27228,7 +27228,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>398.0465935392076</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,16 +27512,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>214.9875889556814</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>214.2389272557618</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -27533,7 +27533,7 @@
         <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>88.44885845517734</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27572,7 +27572,7 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>58.37314290982852</v>
@@ -27597,16 +27597,16 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>305.2431772402318</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27615,13 +27615,13 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>396.1372930982029</v>
+        <v>254.6520681793893</v>
       </c>
       <c r="K4" t="n">
+        <v>266.941429538848</v>
+      </c>
+      <c r="L4" t="n">
         <v>400</v>
-      </c>
-      <c r="L4" t="n">
-        <v>395.9334970102382</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27648,10 +27648,10 @@
         <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9482601269169</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27803,22 +27803,22 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>30.46477465147608</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>318.2903817834539</v>
       </c>
       <c r="X6" t="n">
-        <v>89.97664258953216</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>25.39139276613435</v>
       </c>
     </row>
     <row r="7">
@@ -27828,19 +27828,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27852,10 +27852,10 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>235.1415097211986</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K7" t="n">
-        <v>266.941429538848</v>
+        <v>378.1813610681498</v>
       </c>
       <c r="L7" t="n">
         <v>395.9334970102382</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>209.2309599488807</v>
@@ -27891,13 +27891,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>222.9148456338345</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27992,10 +27992,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>159.5184388018133</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28046,16 +28046,16 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>58.37314290982852</v>
+        <v>147.2444665466435</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>61.45966709731539</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,25 +28065,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>283.0062528954377</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>325.206602576937</v>
       </c>
       <c r="I10" t="n">
         <v>171.047816275856</v>
@@ -28122,19 +28122,19 @@
         <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
+        <v>150.9482601269169</v>
+      </c>
+      <c r="V10" t="n">
         <v>400</v>
-      </c>
-      <c r="V10" t="n">
-        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>94.44753714149141</v>
+        <v>95.83643606459415</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28204,7 +28204,7 @@
         <v>321</v>
       </c>
       <c r="V11" t="n">
-        <v>321</v>
+        <v>319.6111010768973</v>
       </c>
       <c r="W11" t="n">
         <v>321</v>
@@ -28223,25 +28223,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>128.2732823236869</v>
+        <v>128.2732823236865</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
       </c>
       <c r="H12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>191.2065745705938</v>
@@ -28277,7 +28277,7 @@
         <v>321</v>
       </c>
       <c r="T12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>321</v>
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>94.44753714149141</v>
+        <v>94.44753714149138</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28463,7 +28463,7 @@
         <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>321</v>
@@ -28472,7 +28472,7 @@
         <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28511,7 +28511,7 @@
         <v>321</v>
       </c>
       <c r="S15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>321</v>
@@ -28520,16 +28520,16 @@
         <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>128.2732823236869</v>
       </c>
       <c r="Y15" t="n">
-        <v>128.2732823236868</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16">
@@ -28545,7 +28545,7 @@
         <v>321</v>
       </c>
       <c r="D16" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="E16" t="n">
         <v>321</v>
@@ -28593,7 +28593,7 @@
         <v>321</v>
       </c>
       <c r="T16" t="n">
-        <v>309.7843364833203</v>
+        <v>321</v>
       </c>
       <c r="U16" t="n">
         <v>321</v>
@@ -28669,13 +28669,13 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S17" t="n">
-        <v>321</v>
+        <v>319.6111010768973</v>
       </c>
       <c r="T17" t="n">
         <v>321</v>
       </c>
       <c r="U17" t="n">
-        <v>319.6111010768973</v>
+        <v>321</v>
       </c>
       <c r="V17" t="n">
         <v>321</v>
@@ -28697,13 +28697,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
         <v>321</v>
       </c>
       <c r="D18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>321</v>
@@ -28712,13 +28712,13 @@
         <v>321</v>
       </c>
       <c r="G18" t="n">
-        <v>321</v>
+        <v>319.4798568942804</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28754,19 +28754,19 @@
         <v>321</v>
       </c>
       <c r="U18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>321</v>
       </c>
       <c r="W18" t="n">
-        <v>128.273282323687</v>
+        <v>321</v>
       </c>
       <c r="X18" t="n">
         <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
@@ -28842,10 +28842,10 @@
         <v>321</v>
       </c>
       <c r="X19" t="n">
-        <v>321</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="Y19" t="n">
-        <v>309.7843364833204</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20">
@@ -28903,10 +28903,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>162.4939254614603</v>
+        <v>161.1050265383575</v>
       </c>
       <c r="S20" t="n">
-        <v>319.6111010768973</v>
+        <v>321</v>
       </c>
       <c r="T20" t="n">
         <v>321</v>
@@ -28937,13 +28937,13 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>128.2732823236869</v>
+        <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -28982,7 +28982,7 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>321</v>
@@ -28994,13 +28994,13 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>321</v>
+        <v>128.2732823236867</v>
       </c>
       <c r="Y21" t="n">
         <v>321</v>
@@ -29040,7 +29040,7 @@
         <v>321</v>
       </c>
       <c r="K22" t="n">
-        <v>309.7843364833207</v>
+        <v>321</v>
       </c>
       <c r="L22" t="n">
         <v>321</v>
@@ -29067,7 +29067,7 @@
         <v>321</v>
       </c>
       <c r="T22" t="n">
-        <v>321</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U22" t="n">
         <v>321</v>
@@ -29189,10 +29189,10 @@
         <v>321</v>
       </c>
       <c r="H24" t="n">
-        <v>321</v>
+        <v>319.4798568942805</v>
       </c>
       <c r="I24" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29219,7 +29219,7 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>321</v>
@@ -29231,16 +29231,16 @@
         <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>128.2732823236869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29253,7 +29253,7 @@
         <v>321</v>
       </c>
       <c r="C25" t="n">
-        <v>321</v>
+        <v>309.7843364833204</v>
       </c>
       <c r="D25" t="n">
         <v>321</v>
@@ -29271,7 +29271,7 @@
         <v>321</v>
       </c>
       <c r="I25" t="n">
-        <v>309.7843364833205</v>
+        <v>321</v>
       </c>
       <c r="J25" t="n">
         <v>321</v>
@@ -29329,25 +29329,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I26" t="n">
         <v>95.83643606459415</v>
@@ -29377,28 +29377,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>162.4939254614603</v>
+        <v>157.2242265383575</v>
       </c>
       <c r="S26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y26" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27">
@@ -29408,25 +29408,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>128.2732823236871</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>191.2065745705938</v>
@@ -29456,28 +29456,28 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R27" t="n">
-        <v>139.2732823236864</v>
+        <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28">
@@ -29487,76 +29487,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T28" t="n">
-        <v>320</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y28" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29">
@@ -29566,28 +29566,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>95.83643606459415</v>
+        <v>90.56673714149142</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29617,25 +29617,25 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y29" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30">
@@ -29645,25 +29645,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H30" t="n">
-        <v>10.4798568942802</v>
+        <v>319.4798568942804</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -29693,28 +29693,28 @@
         <v>76.98115188293241</v>
       </c>
       <c r="R30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T30" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -29724,76 +29724,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T31" t="n">
-        <v>320</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y31" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32">
@@ -29803,25 +29803,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>95.83643606459415</v>
@@ -29854,25 +29854,25 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S32" t="n">
-        <v>320</v>
+        <v>315.7303010768973</v>
       </c>
       <c r="T32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y32" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33">
@@ -29882,25 +29882,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G33" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H33" t="n">
-        <v>139.2732823236863</v>
+        <v>321</v>
       </c>
       <c r="I33" t="n">
         <v>191.2065745705938</v>
@@ -29927,31 +29927,31 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>76.98115188293241</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V33" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X33" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>320</v>
+        <v>205.2544342066192</v>
       </c>
     </row>
     <row r="34">
@@ -29961,76 +29961,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T34" t="n">
-        <v>320</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="U34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y34" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35">
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>162.4939254614603</v>
+        <v>162.4939254615035</v>
       </c>
       <c r="S35" t="n">
         <v>345</v>
@@ -30119,16 +30119,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>196.8216819483548</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -30140,7 +30140,7 @@
         <v>324.89733246944</v>
       </c>
       <c r="I36" t="n">
-        <v>191.2065745705938</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30173,7 +30173,7 @@
         <v>345</v>
       </c>
       <c r="T36" t="n">
-        <v>341.3006101558915</v>
+        <v>345</v>
       </c>
       <c r="U36" t="n">
         <v>345</v>
@@ -30188,7 +30188,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -30207,7 +30207,7 @@
         <v>345</v>
       </c>
       <c r="E37" t="n">
-        <v>345</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
         <v>345</v>
@@ -30216,19 +30216,19 @@
         <v>345</v>
       </c>
       <c r="H37" t="n">
-        <v>316.56498916343</v>
+        <v>345</v>
       </c>
       <c r="I37" t="n">
+        <v>157.6531277512658</v>
+      </c>
+      <c r="J37" t="n">
         <v>345</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
       <c r="K37" t="n">
-        <v>215.192904948684</v>
+        <v>345</v>
       </c>
       <c r="L37" t="n">
-        <v>329.713201928271</v>
+        <v>345</v>
       </c>
       <c r="M37" t="n">
         <v>345</v>
@@ -30255,16 +30255,16 @@
         <v>345</v>
       </c>
       <c r="U37" t="n">
-        <v>345</v>
+        <v>321.2231078058389</v>
       </c>
       <c r="V37" t="n">
-        <v>345</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
         <v>345</v>
       </c>
       <c r="X37" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
         <v>345</v>
@@ -30362,7 +30362,7 @@
         <v>345</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30374,7 +30374,7 @@
         <v>324.9867056863481</v>
       </c>
       <c r="H39" t="n">
-        <v>321.1979426253319</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>191.2065745705938</v>
@@ -30404,28 +30404,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>345</v>
       </c>
       <c r="T39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>345</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Y39" t="n">
-        <v>345</v>
+        <v>332.8403426253319</v>
       </c>
     </row>
     <row r="40">
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>345</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
         <v>272.7252466480447</v>
@@ -30444,16 +30444,16 @@
         <v>345</v>
       </c>
       <c r="E40" t="n">
+        <v>286.1776220705611</v>
+      </c>
+      <c r="F40" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G40" t="n">
         <v>345</v>
       </c>
-      <c r="F40" t="n">
-        <v>345</v>
-      </c>
-      <c r="G40" t="n">
-        <v>321.4678224996488</v>
-      </c>
       <c r="H40" t="n">
-        <v>345</v>
+        <v>223.1596506917826</v>
       </c>
       <c r="I40" t="n">
         <v>345</v>
@@ -30465,7 +30465,7 @@
         <v>345</v>
       </c>
       <c r="L40" t="n">
-        <v>345</v>
+        <v>329.713201928271</v>
       </c>
       <c r="M40" t="n">
         <v>345</v>
@@ -30495,16 +30495,16 @@
         <v>150.9239650449497</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>345</v>
       </c>
       <c r="W40" t="n">
         <v>345</v>
       </c>
       <c r="X40" t="n">
-        <v>247.4436454301076</v>
+        <v>345</v>
       </c>
       <c r="Y40" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41">
@@ -30514,25 +30514,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
         <v>95.83643606459415</v>
@@ -30565,25 +30565,25 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y41" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42">
@@ -30593,28 +30593,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>94.69956244206298</v>
+        <v>321</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.2065745705938</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,31 +30638,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R42" t="n">
-        <v>320</v>
+        <v>147.1542359885374</v>
       </c>
       <c r="S42" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y42" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43">
@@ -30672,76 +30672,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J43" t="n">
-        <v>320</v>
+        <v>309.7843364833203</v>
       </c>
       <c r="K43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="44">
@@ -30751,25 +30751,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I44" t="n">
         <v>95.83643606459415</v>
@@ -30802,25 +30802,25 @@
         <v>162.4939254614603</v>
       </c>
       <c r="S44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y44" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45">
@@ -30830,25 +30830,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>223.4929878714692</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>191.2065745705938</v>
@@ -30875,31 +30875,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>76.98115188293241</v>
       </c>
       <c r="R45" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S45" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T45" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V45" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>320</v>
+        <v>147.1542359885374</v>
       </c>
       <c r="Y45" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="S46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T46" t="n">
-        <v>320</v>
+        <v>309.7843364833205</v>
       </c>
       <c r="U46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="W46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="X46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y46" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -34743,19 +34743,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>374</v>
+        <v>299.6321147587162</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>299.5314174862185</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34883,16 +34883,16 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>19.70695918467627</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>172.8802509475617</v>
@@ -34901,13 +34901,13 @@
         <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>232.5147750811865</v>
       </c>
       <c r="K4" t="n">
-        <v>133.058570461152</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34934,10 +34934,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -35114,19 +35114,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>155.141864863388</v>
@@ -35138,10 +35138,10 @@
         <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>213.0042166229958</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.2399315293019</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -35177,13 +35177,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,10 +35217,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1006972724976123</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>299.6321147587161</v>
       </c>
       <c r="L8" t="n">
         <v>374</v>
@@ -35232,7 +35232,7 @@
         <v>374</v>
       </c>
       <c r="O8" t="n">
-        <v>299.5314174862185</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>59.25677413017286</v>
@@ -35311,7 +35311,7 @@
         <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>294.168729449915</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
         <v>155.9717969674834</v>
@@ -35351,25 +35351,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2.025348058481198</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8802509475617</v>
+        <v>98.08685352449866</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0517398730831</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,19 +35457,19 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K11" t="n">
-        <v>649</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L11" t="n">
-        <v>649.0000000000001</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M11" t="n">
-        <v>169.5323468034707</v>
+        <v>584.3332209479717</v>
       </c>
       <c r="N11" t="n">
         <v>649</v>
       </c>
       <c r="O11" t="n">
-        <v>166.8217284158573</v>
+        <v>649</v>
       </c>
       <c r="P11" t="n">
         <v>202.0463570447457</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K14" t="n">
-        <v>442.25425142598</v>
+        <v>316.3597287464862</v>
       </c>
       <c r="L14" t="n">
+        <v>222.040703517588</v>
+      </c>
+      <c r="M14" t="n">
         <v>649</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>166.8217284158573</v>
+        <v>649</v>
       </c>
       <c r="P14" t="n">
-        <v>202.0463570447457</v>
+        <v>649</v>
       </c>
       <c r="Q14" t="n">
-        <v>594.9733587913345</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35831,7 +35831,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D16" t="n">
-        <v>35.46378194444452</v>
+        <v>24.24811842776494</v>
       </c>
       <c r="E16" t="n">
         <v>40.01909516304346</v>
@@ -35840,10 +35840,10 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G16" t="n">
-        <v>76.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H16" t="n">
-        <v>97.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I16" t="n">
         <v>163.3468722487342</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>102.456491288538</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U16" t="n">
         <v>170.0760349550503</v>
@@ -35931,13 +35931,13 @@
         <v>514.6820820998604</v>
       </c>
       <c r="K17" t="n">
-        <v>648.9999999999999</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L17" t="n">
-        <v>388.2276102173143</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>41.23339715462306</v>
       </c>
       <c r="N17" t="n">
         <v>649</v>
@@ -35949,7 +35949,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36128,10 +36128,10 @@
         <v>94.62719016129032</v>
       </c>
       <c r="X19" t="n">
-        <v>73.55635456989245</v>
+        <v>62.34069105321293</v>
       </c>
       <c r="Y19" t="n">
-        <v>22.31898363385807</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="20">
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K20" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
+        <v>649.0000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>649</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
-        <v>166.8217284158573</v>
+        <v>336.354075219328</v>
       </c>
       <c r="P20" t="n">
         <v>202.0463570447457</v>
       </c>
       <c r="Q20" t="n">
-        <v>388.2276102173143</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36326,7 +36326,7 @@
         <v>330.3531823116332</v>
       </c>
       <c r="K22" t="n">
-        <v>94.59143153463661</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>113.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U22" t="n">
         <v>170.0760349550503</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K23" t="n">
         <v>178.9801507537688</v>
       </c>
       <c r="L23" t="n">
-        <v>639.5521960497022</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M23" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>649</v>
       </c>
       <c r="O23" t="n">
-        <v>166.8217284158573</v>
+        <v>356.0748414065604</v>
       </c>
       <c r="P23" t="n">
-        <v>202.0463570447457</v>
+        <v>649</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36539,7 +36539,7 @@
         <v>33.88619966292134</v>
       </c>
       <c r="C25" t="n">
-        <v>48.27475335195533</v>
+        <v>37.05908983527576</v>
       </c>
       <c r="D25" t="n">
         <v>35.46378194444452</v>
@@ -36557,7 +36557,7 @@
         <v>97.84034930821744</v>
       </c>
       <c r="I25" t="n">
-        <v>152.1312087320547</v>
+        <v>163.3468722487342</v>
       </c>
       <c r="J25" t="n">
         <v>330.3531823116332</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>514.6820820998604</v>
+        <v>309.8959294854363</v>
       </c>
       <c r="K26" t="n">
-        <v>652.0000000000001</v>
+        <v>650</v>
       </c>
       <c r="L26" t="n">
-        <v>451.1330393047676</v>
+        <v>650</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -36773,34 +36773,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32.88619966292134</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C28" t="n">
-        <v>47.27475335195533</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D28" t="n">
-        <v>34.46378194444452</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E28" t="n">
-        <v>39.01909516304346</v>
+        <v>40.01909516304346</v>
       </c>
       <c r="F28" t="n">
-        <v>45.61714403225807</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G28" t="n">
-        <v>75.58727469945357</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H28" t="n">
-        <v>96.84034930821745</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I28" t="n">
-        <v>162.3468722487342</v>
+        <v>163.3468722487342</v>
       </c>
       <c r="J28" t="n">
-        <v>329.3531823116332</v>
+        <v>330.3531823116332</v>
       </c>
       <c r="K28" t="n">
-        <v>104.807095051316</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36827,22 +36827,22 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>112.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U28" t="n">
-        <v>169.0760349550503</v>
+        <v>170.0760349550503</v>
       </c>
       <c r="V28" t="n">
-        <v>120.8296897837838</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W28" t="n">
-        <v>93.62719016129032</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X28" t="n">
-        <v>72.55635456989245</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y28" t="n">
-        <v>32.53464715053764</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="29">
@@ -36879,25 +36879,25 @@
         <v>514.6820820998604</v>
       </c>
       <c r="K29" t="n">
-        <v>394.106398096102</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L29" t="n">
-        <v>652</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="O29" t="n">
-        <v>166.8217284158573</v>
+        <v>211.0147215300763</v>
       </c>
       <c r="P29" t="n">
         <v>202.0463570447457</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>594.9733587913345</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37010,34 +37010,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32.88619966292134</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C31" t="n">
-        <v>47.27475335195533</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>34.46378194444452</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E31" t="n">
-        <v>39.01909516304346</v>
+        <v>40.01909516304346</v>
       </c>
       <c r="F31" t="n">
-        <v>45.61714403225807</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G31" t="n">
-        <v>75.58727469945357</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H31" t="n">
-        <v>96.84034930821745</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I31" t="n">
-        <v>162.3468722487342</v>
+        <v>163.3468722487342</v>
       </c>
       <c r="J31" t="n">
-        <v>329.3531823116332</v>
+        <v>330.3531823116332</v>
       </c>
       <c r="K31" t="n">
-        <v>104.807095051316</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37064,22 +37064,22 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>112.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U31" t="n">
-        <v>169.0760349550503</v>
+        <v>170.0760349550503</v>
       </c>
       <c r="V31" t="n">
-        <v>120.8296897837838</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W31" t="n">
-        <v>93.62719016129032</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X31" t="n">
-        <v>72.55635456989245</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y31" t="n">
-        <v>32.53464715053764</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="32">
@@ -37113,25 +37113,25 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>84.37734551370366</v>
+        <v>254.8692882767706</v>
       </c>
       <c r="K32" t="n">
-        <v>541.2792201428621</v>
+        <v>650</v>
       </c>
       <c r="L32" t="n">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="O32" t="n">
-        <v>652</v>
+        <v>166.8217284158573</v>
       </c>
       <c r="P32" t="n">
-        <v>652</v>
+        <v>202.0463570447457</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37247,34 +37247,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>32.88619966292134</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C34" t="n">
-        <v>47.27475335195533</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D34" t="n">
-        <v>34.46378194444452</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E34" t="n">
-        <v>39.01909516304346</v>
+        <v>40.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>45.61714403225807</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G34" t="n">
-        <v>75.58727469945357</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H34" t="n">
-        <v>96.84034930821745</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I34" t="n">
-        <v>162.3468722487342</v>
+        <v>163.3468722487342</v>
       </c>
       <c r="J34" t="n">
-        <v>329.3531823116332</v>
+        <v>330.3531823116332</v>
       </c>
       <c r="K34" t="n">
-        <v>104.807095051316</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37301,22 +37301,22 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>112.6721548052177</v>
+        <v>102.456491288538</v>
       </c>
       <c r="U34" t="n">
-        <v>169.0760349550503</v>
+        <v>170.0760349550503</v>
       </c>
       <c r="V34" t="n">
-        <v>120.8296897837838</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W34" t="n">
-        <v>93.62719016129032</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X34" t="n">
-        <v>72.55635456989245</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y34" t="n">
-        <v>32.53464715053764</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="35">
@@ -37353,25 +37353,25 @@
         <v>84.37734551370366</v>
       </c>
       <c r="K35" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>562.0000000000001</v>
+        <v>558.9999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>86.0474983186226</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>166.8217284158573</v>
+        <v>249.9904388556834</v>
       </c>
       <c r="P35" t="n">
         <v>202.0463570447457</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>559.0000000000089</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37435,7 +37435,7 @@
         <v>312.6694206785272</v>
       </c>
       <c r="L36" t="n">
-        <v>430.1657553842807</v>
+        <v>418.2869675055369</v>
       </c>
       <c r="M36" t="n">
         <v>277.7000421645042</v>
@@ -37493,7 +37493,7 @@
         <v>59.46378194444452</v>
       </c>
       <c r="E37" t="n">
-        <v>64.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>70.61714403225807</v>
@@ -37502,19 +37502,19 @@
         <v>100.5872746994536</v>
       </c>
       <c r="H37" t="n">
-        <v>93.40533847164743</v>
+        <v>121.8403493082175</v>
       </c>
       <c r="I37" t="n">
-        <v>187.3468722487342</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>9.353182311633219</v>
+        <v>354.3531823116332</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>129.807095051316</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>15.28679807172902</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37541,16 +37541,16 @@
         <v>137.6721548052177</v>
       </c>
       <c r="U37" t="n">
-        <v>194.0760349550503</v>
+        <v>170.2991427608892</v>
       </c>
       <c r="V37" t="n">
-        <v>145.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>118.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>57.53464715053764</v>
@@ -37587,16 +37587,16 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>514.6820820998604</v>
+        <v>167.5460559535149</v>
       </c>
       <c r="K38" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>217.7427617324659</v>
+        <v>559.0000000000234</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -37666,7 +37666,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>188.9490240091185</v>
+        <v>196.3345496339022</v>
       </c>
       <c r="K39" t="n">
         <v>312.6694206785272</v>
@@ -37684,7 +37684,7 @@
         <v>420.5744747329351</v>
       </c>
       <c r="P39" t="n">
-        <v>257.4235516844645</v>
+        <v>238.1592381808931</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -37730,16 +37730,16 @@
         <v>59.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>64.01909516304346</v>
+        <v>5.196717233604542</v>
       </c>
       <c r="F40" t="n">
-        <v>70.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>77.05509719910241</v>
+        <v>100.5872746994536</v>
       </c>
       <c r="H40" t="n">
-        <v>121.8403493082174</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>187.3468722487342</v>
@@ -37751,7 +37751,7 @@
         <v>129.807095051316</v>
       </c>
       <c r="L40" t="n">
-        <v>15.28679807172904</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -37781,16 +37781,16 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>145.8296897837838</v>
       </c>
       <c r="W40" t="n">
         <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>97.55635456989245</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="41">
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>514.6820820998604</v>
+        <v>84.37734551370366</v>
       </c>
       <c r="K41" t="n">
-        <v>217.742761732466</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>561.9999999999999</v>
+        <v>558.9999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>83.16871043979693</v>
       </c>
       <c r="O41" t="n">
         <v>166.8217284158573</v>
@@ -37845,7 +37845,7 @@
         <v>202.0463570447457</v>
       </c>
       <c r="Q41" t="n">
-        <v>562</v>
+        <v>559.000000000038</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,7 +37903,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>188.9490240091185</v>
+        <v>196.3345496339022</v>
       </c>
       <c r="K42" t="n">
         <v>312.6694206785272</v>
@@ -37912,7 +37912,7 @@
         <v>437.5512810090644</v>
       </c>
       <c r="M42" t="n">
-        <v>277.7000421645042</v>
+        <v>258.4357286609326</v>
       </c>
       <c r="N42" t="n">
         <v>330.4251350143152</v>
@@ -37958,34 +37958,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.88619966292134</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C43" t="n">
-        <v>47.27475335195533</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D43" t="n">
-        <v>34.46378194444452</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E43" t="n">
-        <v>39.01909516304346</v>
+        <v>40.01909516304346</v>
       </c>
       <c r="F43" t="n">
-        <v>45.61714403225807</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G43" t="n">
-        <v>75.58727469945357</v>
+        <v>76.58727469945359</v>
       </c>
       <c r="H43" t="n">
-        <v>96.84034930821745</v>
+        <v>97.84034930821744</v>
       </c>
       <c r="I43" t="n">
-        <v>162.3468722487342</v>
+        <v>163.3468722487342</v>
       </c>
       <c r="J43" t="n">
-        <v>329.3531823116332</v>
+        <v>319.1375187949535</v>
       </c>
       <c r="K43" t="n">
-        <v>104.807095051316</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,22 +38012,22 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>112.6721548052177</v>
+        <v>113.6721548052177</v>
       </c>
       <c r="U43" t="n">
-        <v>169.0760349550503</v>
+        <v>170.0760349550503</v>
       </c>
       <c r="V43" t="n">
-        <v>120.8296897837838</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W43" t="n">
-        <v>93.62719016129032</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X43" t="n">
-        <v>72.55635456989245</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y43" t="n">
-        <v>32.53464715053764</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
     <row r="44">
@@ -38061,22 +38061,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>84.37734551370366</v>
+        <v>514.6820820998604</v>
       </c>
       <c r="K44" t="n">
-        <v>562</v>
+        <v>178.9801507537688</v>
       </c>
       <c r="L44" t="n">
-        <v>562.0000000000001</v>
+        <v>222.040703517588</v>
       </c>
       <c r="M44" t="n">
-        <v>562</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>86.0474983186226</v>
+        <v>536.6648479981114</v>
       </c>
       <c r="O44" t="n">
-        <v>166.8217284158573</v>
+        <v>559.0000000000671</v>
       </c>
       <c r="P44" t="n">
         <v>202.0463570447457</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>188.9490240091185</v>
+        <v>196.3345496339022</v>
       </c>
       <c r="K45" t="n">
         <v>312.6694206785272</v>
@@ -38152,7 +38152,7 @@
         <v>277.7000421645042</v>
       </c>
       <c r="N45" t="n">
-        <v>330.4251350143152</v>
+        <v>311.1608215107437</v>
       </c>
       <c r="O45" t="n">
         <v>420.5744747329351</v>
@@ -38195,34 +38195,34 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32.88619966292134</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>47.27475335195533</v>
+        <v>48.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>34.46378194444452</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>39.01909516304346</v>
+        <v>40.01909516304346</v>
       </c>
       <c r="F46" t="n">
-        <v>45.61714403225807</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>75.58727469945359</v>
+        <v>76.58727469945357</v>
       </c>
       <c r="H46" t="n">
-        <v>96.84034930821744</v>
+        <v>97.84034930821745</v>
       </c>
       <c r="I46" t="n">
-        <v>162.3468722487342</v>
+        <v>163.3468722487342</v>
       </c>
       <c r="J46" t="n">
-        <v>329.3531823116332</v>
+        <v>330.3531823116332</v>
       </c>
       <c r="K46" t="n">
-        <v>104.807095051316</v>
+        <v>105.807095051316</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,22 +38249,22 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>112.6721548052177</v>
+        <v>102.4564912885382</v>
       </c>
       <c r="U46" t="n">
-        <v>169.0760349550503</v>
+        <v>170.0760349550503</v>
       </c>
       <c r="V46" t="n">
-        <v>120.8296897837838</v>
+        <v>121.8296897837838</v>
       </c>
       <c r="W46" t="n">
-        <v>93.62719016129032</v>
+        <v>94.62719016129032</v>
       </c>
       <c r="X46" t="n">
-        <v>72.55635456989245</v>
+        <v>73.55635456989245</v>
       </c>
       <c r="Y46" t="n">
-        <v>32.53464715053764</v>
+        <v>33.53464715053764</v>
       </c>
     </row>
   </sheetData>
